--- a/Groups_Module/Groups_Module_Test_Cases.xlsx
+++ b/Groups_Module/Groups_Module_Test_Cases.xlsx
@@ -2,8 +2,18 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
   <sheets>
-    <sheet name="Groups Module Test Cases" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Functional" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Integration" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Regression" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Security" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Edge Cases" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Boundary Values" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Equivalence Partitioning" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -13,90 +23,41 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
+      <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <b val="1"/>
-      <color theme="1"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color theme="1"/>
+      <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
-    <font/>
   </fonts>
   <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor rgb="FFFFFF00"/>
+        <fgColor rgb="004472C4"/>
+        <bgColor rgb="004472C4"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
-    <border/>
+  <borders count="2">
     <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin"/>
@@ -108,37 +69,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="bottom"/>
-    </xf>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -211,20 +154,20 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Sheets">
+    <a:clrScheme name="Office">
       <a:dk1>
-        <a:srgbClr val="000000"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="000000"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
         <a:srgbClr val="4F81BD"/>
@@ -248,19 +191,77 @@
         <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Sheets">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -272,159 +273,190 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="004472C4"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H50"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
+  <dimension ref="A1:H32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14.86" customWidth="1" style="7" min="1" max="1"/>
-    <col width="12.71" customWidth="1" style="7" min="2" max="2"/>
-    <col width="25" customWidth="1" style="7" min="3" max="3"/>
-    <col width="29.86" customWidth="1" style="7" min="4" max="4"/>
-    <col width="30" customWidth="1" style="7" min="5" max="5"/>
-    <col width="34" customWidth="1" style="7" min="6" max="6"/>
-    <col width="40" customWidth="1" style="7" min="7" max="7"/>
-    <col width="18" customWidth="1" style="7" min="8" max="8"/>
-    <col width="8.710000000000001" customWidth="1" style="7" min="9" max="26"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="19.5" customHeight="1" s="7">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>TestCase_ID</t>
@@ -472,7 +504,7 @@
           <t>GROUPS_001</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
@@ -516,9 +548,9 @@
           <t>GROUPS_002</t>
         </is>
       </c>
-      <c r="B3" s="9" t="n"/>
-      <c r="C3" s="9" t="n"/>
-      <c r="D3" s="9" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
       <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Verify group name display</t>
@@ -547,9 +579,9 @@
           <t>GROUPS_003</t>
         </is>
       </c>
-      <c r="B4" s="9" t="n"/>
-      <c r="C4" s="9" t="n"/>
-      <c r="D4" s="9" t="n"/>
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Verify group avatar/icon display</t>
@@ -578,9 +610,9 @@
           <t>GROUPS_004</t>
         </is>
       </c>
-      <c r="B5" s="9" t="n"/>
-      <c r="C5" s="9" t="n"/>
-      <c r="D5" s="9" t="n"/>
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
       <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Verify member count display</t>
@@ -609,9 +641,9 @@
           <t>GROUPS_005</t>
         </is>
       </c>
-      <c r="B6" s="9" t="n"/>
-      <c r="C6" s="9" t="n"/>
-      <c r="D6" s="9" t="n"/>
+      <c r="B6" s="2" t="n"/>
+      <c r="C6" s="2" t="n"/>
+      <c r="D6" s="2" t="n"/>
       <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Verify online status indicator</t>
@@ -640,9 +672,9 @@
           <t>GROUPS_006</t>
         </is>
       </c>
-      <c r="B7" s="10" t="n"/>
-      <c r="C7" s="10" t="n"/>
-      <c r="D7" s="10" t="n"/>
+      <c r="B7" s="2" t="n"/>
+      <c r="C7" s="2" t="n"/>
+      <c r="D7" s="2" t="n"/>
       <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Verify group initials avatar display</t>
@@ -671,7 +703,7 @@
           <t>GROUPS_007</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
@@ -714,8 +746,8 @@
           <t>GROUPS_008</t>
         </is>
       </c>
-      <c r="B9" s="10" t="n"/>
-      <c r="C9" s="10" t="n"/>
+      <c r="B9" s="2" t="n"/>
+      <c r="C9" s="2" t="n"/>
       <c r="D9" s="2" t="inlineStr">
         <is>
           <t>User is logged in, group has very long name</t>
@@ -794,7 +826,7 @@
           <t>GROUPS_010</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
@@ -837,9 +869,9 @@
           <t>GROUPS_011</t>
         </is>
       </c>
-      <c r="B12" s="9" t="n"/>
-      <c r="C12" s="9" t="n"/>
-      <c r="D12" s="9" t="n"/>
+      <c r="B12" s="2" t="n"/>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="2" t="n"/>
       <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Verify search by group name</t>
@@ -869,9 +901,9 @@
           <t>GROUPS_012</t>
         </is>
       </c>
-      <c r="B13" s="9" t="n"/>
-      <c r="C13" s="9" t="n"/>
-      <c r="D13" s="9" t="n"/>
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="2" t="n"/>
+      <c r="D13" s="2" t="n"/>
       <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Verify search by partial name</t>
@@ -901,9 +933,9 @@
           <t>GROUPS_013</t>
         </is>
       </c>
-      <c r="B14" s="9" t="n"/>
-      <c r="C14" s="9" t="n"/>
-      <c r="D14" s="9" t="n"/>
+      <c r="B14" s="2" t="n"/>
+      <c r="C14" s="2" t="n"/>
+      <c r="D14" s="2" t="n"/>
       <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Verify case-insensitive search</t>
@@ -933,9 +965,9 @@
           <t>GROUPS_014</t>
         </is>
       </c>
-      <c r="B15" s="9" t="n"/>
-      <c r="C15" s="9" t="n"/>
-      <c r="D15" s="9" t="n"/>
+      <c r="B15" s="2" t="n"/>
+      <c r="C15" s="2" t="n"/>
+      <c r="D15" s="2" t="n"/>
       <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Verify clearing search field</t>
@@ -965,9 +997,9 @@
           <t>GROUPS_015</t>
         </is>
       </c>
-      <c r="B16" s="10" t="n"/>
-      <c r="C16" s="10" t="n"/>
-      <c r="D16" s="10" t="n"/>
+      <c r="B16" s="2" t="n"/>
+      <c r="C16" s="2" t="n"/>
+      <c r="D16" s="2" t="n"/>
       <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Verify real-time search filtering</t>
@@ -997,7 +1029,7 @@
           <t>GROUPS_016</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
@@ -1041,9 +1073,9 @@
           <t>GROUPS_017</t>
         </is>
       </c>
-      <c r="B18" s="10" t="n"/>
-      <c r="C18" s="10" t="n"/>
-      <c r="D18" s="10" t="n"/>
+      <c r="B18" s="2" t="n"/>
+      <c r="C18" s="2" t="n"/>
+      <c r="D18" s="2" t="n"/>
       <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Verify search with special characters</t>
@@ -1073,7 +1105,7 @@
           <t>GROUPS_018</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
@@ -1117,9 +1149,9 @@
           <t>GROUPS_019</t>
         </is>
       </c>
-      <c r="B20" s="10" t="n"/>
-      <c r="C20" s="10" t="n"/>
-      <c r="D20" s="10" t="n"/>
+      <c r="B20" s="2" t="n"/>
+      <c r="C20" s="2" t="n"/>
+      <c r="D20" s="2" t="n"/>
       <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Verify selected group visual feedback</t>
@@ -1143,13 +1175,13 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="15.75" customHeight="1" s="7">
+    <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
           <t>GROUPS_020</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
@@ -1186,15 +1218,15 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="15.75" customHeight="1" s="7">
+    <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
           <t>GROUPS_021</t>
         </is>
       </c>
-      <c r="B22" s="9" t="n"/>
-      <c r="C22" s="9" t="n"/>
-      <c r="D22" s="9" t="n"/>
+      <c r="B22" s="2" t="n"/>
+      <c r="C22" s="2" t="n"/>
+      <c r="D22" s="2" t="n"/>
       <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Verify Create Group button click</t>
@@ -1218,15 +1250,15 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="15.75" customHeight="1" s="7">
+    <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
           <t>GROUPS_022</t>
         </is>
       </c>
-      <c r="B23" s="10" t="n"/>
-      <c r="C23" s="10" t="n"/>
-      <c r="D23" s="10" t="n"/>
+      <c r="B23" s="2" t="n"/>
+      <c r="C23" s="2" t="n"/>
+      <c r="D23" s="2" t="n"/>
       <c r="E23" s="2" t="inlineStr">
         <is>
           <t>Verify Create Group button hover state</t>
@@ -1250,13 +1282,13 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="15.75" customHeight="1" s="7">
+    <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
           <t>GROUPS_023</t>
         </is>
       </c>
-      <c r="B24" s="8" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
@@ -1293,15 +1325,15 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="15.75" customHeight="1" s="7">
+    <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
           <t>GROUPS_024</t>
         </is>
       </c>
-      <c r="B25" s="9" t="n"/>
-      <c r="C25" s="9" t="n"/>
-      <c r="D25" s="9" t="n"/>
+      <c r="B25" s="2" t="n"/>
+      <c r="C25" s="2" t="n"/>
+      <c r="D25" s="2" t="n"/>
       <c r="E25" s="2" t="inlineStr">
         <is>
           <t>Verify welcome message instruction text</t>
@@ -1324,15 +1356,15 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="15.75" customHeight="1" s="7">
+    <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
           <t>GROUPS_025</t>
         </is>
       </c>
-      <c r="B26" s="10" t="n"/>
-      <c r="C26" s="10" t="n"/>
-      <c r="D26" s="10" t="n"/>
+      <c r="B26" s="2" t="n"/>
+      <c r="C26" s="2" t="n"/>
+      <c r="D26" s="2" t="n"/>
       <c r="E26" s="2" t="inlineStr">
         <is>
           <t>Verify welcome message icon</t>
@@ -1355,13 +1387,13 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="15.75" customHeight="1" s="7">
+    <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
           <t>GROUPS_026</t>
         </is>
       </c>
-      <c r="B27" s="8" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
@@ -1399,15 +1431,15 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="15.75" customHeight="1" s="7">
+    <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
           <t>GROUPS_027</t>
         </is>
       </c>
-      <c r="B28" s="10" t="n"/>
-      <c r="C28" s="10" t="n"/>
-      <c r="D28" s="10" t="n"/>
+      <c r="B28" s="2" t="n"/>
+      <c r="C28" s="2" t="n"/>
+      <c r="D28" s="2" t="n"/>
       <c r="E28" s="2" t="inlineStr">
         <is>
           <t>Verify Groups module on mobile device</t>
@@ -1431,13 +1463,13 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="15.75" customHeight="1" s="7">
+    <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
           <t>GROUPS_028</t>
         </is>
       </c>
-      <c r="B29" s="8" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
@@ -1474,15 +1506,15 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="15.75" customHeight="1" s="7">
+    <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
           <t>GROUPS_029</t>
         </is>
       </c>
-      <c r="B30" s="10" t="n"/>
-      <c r="C30" s="10" t="n"/>
-      <c r="D30" s="10" t="n"/>
+      <c r="B30" s="2" t="n"/>
+      <c r="C30" s="2" t="n"/>
+      <c r="D30" s="2" t="n"/>
       <c r="E30" s="2" t="inlineStr">
         <is>
           <t>Verify navigation between tabs</t>
@@ -1506,13 +1538,13 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="15.75" customHeight="1" s="7">
+    <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
           <t>GROUPS_030</t>
         </is>
       </c>
-      <c r="B31" s="8" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
@@ -1550,14 +1582,14 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="15.75" customHeight="1" s="7">
+    <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
           <t>GROUPS_031</t>
         </is>
       </c>
-      <c r="B32" s="10" t="n"/>
-      <c r="C32" s="10" t="n"/>
+      <c r="B32" s="2" t="n"/>
+      <c r="C32" s="2" t="n"/>
       <c r="D32" s="2" t="inlineStr">
         <is>
           <t>User is logged in, network error</t>
@@ -1586,1622 +1618,1043 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="15.75" customHeight="1" s="7">
-      <c r="A33" s="11" t="inlineStr">
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="0070AD47"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TestCase_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Sentiment</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Precondition</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Expected Results</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Priority / Severity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>GROUPS_032</t>
         </is>
       </c>
-      <c r="B33" s="11" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C33" s="11" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Integration: Groups Module with Chat</t>
         </is>
       </c>
-      <c r="D33" s="11" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>User is logged in and on Groups tab</t>
         </is>
       </c>
-      <c r="E33" s="11" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Verify clicking group opens group chat</t>
         </is>
       </c>
-      <c r="F33" s="11" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>1. Click on a group in the list.
 2. Observe chat area.</t>
         </is>
       </c>
-      <c r="G33" s="11" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Group chat should open with message history and group header info.</t>
         </is>
       </c>
-      <c r="H33" s="11" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="15.75" customHeight="1" s="7">
-      <c r="A34" s="11" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>GROUPS_033</t>
         </is>
       </c>
-      <c r="B34" s="11" t="inlineStr"/>
-      <c r="C34" s="11" t="inlineStr">
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Integration: Groups Module with Group Actions</t>
         </is>
       </c>
-      <c r="D34" s="11" t="inlineStr"/>
-      <c r="E34" s="11" t="inlineStr">
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Verify group info accessible from group list</t>
         </is>
       </c>
-      <c r="F34" s="11" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>1. Long press or click info on a group in the list.</t>
         </is>
       </c>
-      <c r="G34" s="11" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Group info/actions panel should open.</t>
         </is>
       </c>
-      <c r="H34" s="11" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="15.75" customHeight="1" s="7">
-      <c r="A35" s="11" t="inlineStr">
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00FFC000"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TestCase_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Sentiment</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Precondition</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Expected Results</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Priority / Severity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>GROUPS_034</t>
         </is>
       </c>
-      <c r="B35" s="11" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C35" s="11" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Regression: Groups Module</t>
         </is>
       </c>
-      <c r="D35" s="11" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E35" s="11" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Verify group list updates after creating a new group</t>
         </is>
       </c>
-      <c r="F35" s="11" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>1. Create a new group.
 2. Go back to group list.</t>
         </is>
       </c>
-      <c r="G35" s="11" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Newly created group should appear in the list.</t>
         </is>
       </c>
-      <c r="H35" s="11" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="15.75" customHeight="1" s="7">
-      <c r="A36" s="11" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>GROUPS_035</t>
         </is>
       </c>
-      <c r="B36" s="11" t="inlineStr"/>
-      <c r="C36" s="11" t="inlineStr"/>
-      <c r="D36" s="11" t="inlineStr"/>
-      <c r="E36" s="11" t="inlineStr">
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Verify group list updates after leaving a group</t>
         </is>
       </c>
-      <c r="F36" s="11" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>1. Leave a group.
 2. Observe group list.</t>
         </is>
       </c>
-      <c r="G36" s="11" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Left group should be removed from the list or marked appropriately.</t>
         </is>
       </c>
-      <c r="H36" s="11" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="15.75" customHeight="1" s="7">
-      <c r="A37" s="11" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>GROUPS_036</t>
         </is>
       </c>
-      <c r="B37" s="11" t="inlineStr"/>
-      <c r="C37" s="11" t="inlineStr"/>
-      <c r="D37" s="11" t="inlineStr"/>
-      <c r="E37" s="11" t="inlineStr">
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Verify group list after deleting a group</t>
         </is>
       </c>
-      <c r="F37" s="11" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>1. Delete a group (as owner).
 2. Observe group list.</t>
         </is>
       </c>
-      <c r="G37" s="11" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Deleted group should be removed from the list for all members.</t>
         </is>
       </c>
-      <c r="H37" s="11" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="15.75" customHeight="1" s="7">
-      <c r="A38" s="11" t="inlineStr">
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00FF0000"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TestCase_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Sentiment</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Precondition</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Expected Results</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Priority / Severity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>GROUPS_037</t>
         </is>
       </c>
-      <c r="B38" s="11" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C38" s="11" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Security: Groups Module</t>
         </is>
       </c>
-      <c r="D38" s="11" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E38" s="11" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Verify private groups not visible to non-members</t>
         </is>
       </c>
-      <c r="F38" s="11" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>1. Observe group list as a non-member.</t>
         </is>
       </c>
-      <c r="G38" s="11" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Private groups should not appear in the group list for non-members.</t>
         </is>
       </c>
-      <c r="H38" s="11" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>High / Critical</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="15.75" customHeight="1" s="7">
-      <c r="A39" s="11" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>GROUPS_038</t>
         </is>
       </c>
-      <c r="B39" s="11" t="inlineStr"/>
-      <c r="C39" s="11" t="inlineStr"/>
-      <c r="D39" s="11" t="inlineStr"/>
-      <c r="E39" s="11" t="inlineStr">
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Verify password-protected group requires password to join</t>
         </is>
       </c>
-      <c r="F39" s="11" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>1. Click join on a password-protected group.
 2. Enter wrong password.</t>
         </is>
       </c>
-      <c r="G39" s="11" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Should reject with 'Incorrect password' error. Should not allow entry.</t>
         </is>
       </c>
-      <c r="H39" s="11" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>High / Critical</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="15.75" customHeight="1" s="7">
-      <c r="A40" s="11" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>GROUPS_039</t>
         </is>
       </c>
-      <c r="B40" s="11" t="inlineStr"/>
-      <c r="C40" s="11" t="inlineStr"/>
-      <c r="D40" s="11" t="inlineStr"/>
-      <c r="E40" s="11" t="inlineStr">
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Verify group creation validates input</t>
         </is>
       </c>
-      <c r="F40" s="11" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>1. Try to create a group with empty name.
 2. Try with special characters.
 3. Try with very long name.</t>
         </is>
       </c>
-      <c r="G40" s="11" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Empty name should be rejected. Special chars should be handled. Long name should truncate or reject.</t>
         </is>
       </c>
-      <c r="H40" s="11" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="15.75" customHeight="1" s="7">
-      <c r="A41" s="11" t="inlineStr">
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00ED7D31"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TestCase_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Sentiment</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Precondition</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Expected Results</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Priority / Severity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>GROUPS_040</t>
         </is>
       </c>
-      <c r="B41" s="11" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C41" s="11" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Edge Case: Groups Module</t>
         </is>
       </c>
-      <c r="D41" s="11" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E41" s="11" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Verify group list with 500+ groups</t>
         </is>
       </c>
-      <c r="F41" s="11" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>1. Have an account that's part of 500+ groups.
 2. Open groups tab.</t>
         </is>
       </c>
-      <c r="G41" s="11" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Groups should load with pagination/infinite scroll. No performance issues.</t>
         </is>
       </c>
-      <c r="H41" s="11" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Medium / High</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="15.75" customHeight="1" s="7">
-      <c r="A42" s="11" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>GROUPS_041</t>
         </is>
       </c>
-      <c r="B42" s="11" t="inlineStr"/>
-      <c r="C42" s="11" t="inlineStr"/>
-      <c r="D42" s="11" t="inlineStr"/>
-      <c r="E42" s="11" t="inlineStr">
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Verify creating group with duplicate name</t>
         </is>
       </c>
-      <c r="F42" s="11" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>1. Create a group with a name that already exists.</t>
         </is>
       </c>
-      <c r="G42" s="11" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Should either allow (with different ID) or show warning about duplicate name.</t>
         </is>
       </c>
-      <c r="H42" s="11" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="15.75" customHeight="1" s="7">
-      <c r="A43" s="11" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>GROUPS_042</t>
         </is>
       </c>
-      <c r="B43" s="11" t="inlineStr"/>
-      <c r="C43" s="11" t="inlineStr"/>
-      <c r="D43" s="11" t="inlineStr"/>
-      <c r="E43" s="11" t="inlineStr">
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Verify group with emoji in name</t>
         </is>
       </c>
-      <c r="F43" s="11" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>1. Create a group named '🚀 Rocket Team'.
 2. Observe in group list.</t>
         </is>
       </c>
-      <c r="G43" s="11" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Group name with emoji should display correctly.</t>
         </is>
       </c>
-      <c r="H43" s="11" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Low / Low</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="15.75" customHeight="1" s="7">
-      <c r="A44" s="11" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>GROUPS_043</t>
         </is>
       </c>
-      <c r="B44" s="11" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C44" s="11" t="inlineStr"/>
-      <c r="D44" s="11" t="inlineStr"/>
-      <c r="E44" s="11" t="inlineStr">
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Verify group creation without network</t>
         </is>
       </c>
-      <c r="F44" s="11" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>1. Disconnect network.
 2. Try to create a group.</t>
         </is>
       </c>
-      <c r="G44" s="11" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Error message should display. Group should not be created.</t>
         </is>
       </c>
-      <c r="H44" s="11" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="15.75" customHeight="1" s="7">
-      <c r="A45" s="11" t="inlineStr">
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="007030A0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TestCase_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Sentiment</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Precondition</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Expected Results</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Priority / Severity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>GROUPS_044</t>
         </is>
       </c>
-      <c r="B45" s="11" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C45" s="11" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Boundary: Groups Module</t>
         </is>
       </c>
-      <c r="D45" s="11" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E45" s="11" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Verify group list with exactly 0 groups</t>
         </is>
       </c>
-      <c r="F45" s="11" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>1. Login with account not part of any group.</t>
         </is>
       </c>
-      <c r="G45" s="11" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Empty state should display with 'No groups' message and create button.</t>
         </is>
       </c>
-      <c r="H45" s="11" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="15.75" customHeight="1" s="7">
-      <c r="A46" s="11" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>GROUPS_045</t>
         </is>
       </c>
-      <c r="B46" s="11" t="inlineStr"/>
-      <c r="C46" s="11" t="inlineStr"/>
-      <c r="D46" s="11" t="inlineStr"/>
-      <c r="E46" s="11" t="inlineStr">
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Verify group name with exactly 1 character</t>
         </is>
       </c>
-      <c r="F46" s="11" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>1. Create a group with name 'A'.</t>
         </is>
       </c>
-      <c r="G46" s="11" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Group should be created successfully with single character name.</t>
         </is>
       </c>
-      <c r="H46" s="11" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Low / Low</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="15.75" customHeight="1" s="7">
-      <c r="A47" s="11" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>GROUPS_046</t>
         </is>
       </c>
-      <c r="B47" s="11" t="inlineStr"/>
-      <c r="C47" s="11" t="inlineStr"/>
-      <c r="D47" s="11" t="inlineStr"/>
-      <c r="E47" s="11" t="inlineStr">
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Verify group name at maximum length</t>
         </is>
       </c>
-      <c r="F47" s="11" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>1. Create a group with name at max character limit.</t>
         </is>
       </c>
-      <c r="G47" s="11" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Group should be created. Name should display (possibly truncated in list).</t>
         </is>
       </c>
-      <c r="H47" s="11" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="15.75" customHeight="1" s="7">
-      <c r="A48" s="11" t="inlineStr">
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="0000B0F0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TestCase_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Sentiment</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Precondition</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Expected Results</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Priority / Severity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>GROUPS_047</t>
         </is>
       </c>
-      <c r="B48" s="11" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C48" s="11" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Equivalence Partitioning: Group Types</t>
         </is>
       </c>
-      <c r="D48" s="11" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E48" s="11" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Verify public group display and join</t>
         </is>
       </c>
-      <c r="F48" s="11" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>1. Observe a public group in list.
 2. Click join.</t>
         </is>
       </c>
-      <c r="G48" s="11" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Public group should show join button. Joining should be immediate without approval.</t>
         </is>
       </c>
-      <c r="H48" s="11" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="15.75" customHeight="1" s="7">
-      <c r="A49" s="11" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>GROUPS_048</t>
         </is>
       </c>
-      <c r="B49" s="11" t="inlineStr"/>
-      <c r="C49" s="11" t="inlineStr"/>
-      <c r="D49" s="11" t="inlineStr"/>
-      <c r="E49" s="11" t="inlineStr">
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Verify private group display and join</t>
         </is>
       </c>
-      <c r="F49" s="11" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>1. Observe a private group (if visible).
 2. Try to join.</t>
         </is>
       </c>
-      <c r="G49" s="11" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Private group should require invitation. No direct join option.</t>
         </is>
       </c>
-      <c r="H49" s="11" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="15.75" customHeight="1" s="7">
-      <c r="A50" s="11" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>GROUPS_049</t>
         </is>
       </c>
-      <c r="B50" s="11" t="inlineStr"/>
-      <c r="C50" s="11" t="inlineStr"/>
-      <c r="D50" s="11" t="inlineStr"/>
-      <c r="E50" s="11" t="inlineStr">
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Verify password-protected group display and join</t>
         </is>
       </c>
-      <c r="F50" s="11" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>1. Observe a password-protected group.
 2. Click join.
 3. Enter correct password.</t>
         </is>
       </c>
-      <c r="G50" s="11" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Should prompt for password. Correct password should allow joining.</t>
         </is>
       </c>
-      <c r="H50" s="11" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="15.75" customHeight="1" s="7"/>
-    <row r="52" ht="15.75" customHeight="1" s="7"/>
-    <row r="53" ht="15.75" customHeight="1" s="7"/>
-    <row r="54" ht="15.75" customHeight="1" s="7"/>
-    <row r="55" ht="15.75" customHeight="1" s="7"/>
-    <row r="56" ht="15.75" customHeight="1" s="7"/>
-    <row r="57" ht="15.75" customHeight="1" s="7"/>
-    <row r="58" ht="15.75" customHeight="1" s="7"/>
-    <row r="59" ht="15.75" customHeight="1" s="7"/>
-    <row r="60" ht="15.75" customHeight="1" s="7"/>
-    <row r="61" ht="15.75" customHeight="1" s="7"/>
-    <row r="62" ht="15.75" customHeight="1" s="7"/>
-    <row r="63" ht="15.75" customHeight="1" s="7"/>
-    <row r="64" ht="15.75" customHeight="1" s="7"/>
-    <row r="65" ht="15.75" customHeight="1" s="7"/>
-    <row r="66" ht="15.75" customHeight="1" s="7"/>
-    <row r="67" ht="15.75" customHeight="1" s="7"/>
-    <row r="68" ht="15.75" customHeight="1" s="7"/>
-    <row r="69" ht="15.75" customHeight="1" s="7"/>
-    <row r="70" ht="15.75" customHeight="1" s="7"/>
-    <row r="71" ht="15.75" customHeight="1" s="7"/>
-    <row r="72" ht="15.75" customHeight="1" s="7"/>
-    <row r="73" ht="15.75" customHeight="1" s="7"/>
-    <row r="74" ht="15.75" customHeight="1" s="7"/>
-    <row r="75" ht="15.75" customHeight="1" s="7"/>
-    <row r="76" ht="15.75" customHeight="1" s="7"/>
-    <row r="77" ht="15.75" customHeight="1" s="7"/>
-    <row r="78" ht="15.75" customHeight="1" s="7"/>
-    <row r="79" ht="15.75" customHeight="1" s="7"/>
-    <row r="80" ht="15.75" customHeight="1" s="7"/>
-    <row r="81" ht="15.75" customHeight="1" s="7"/>
-    <row r="82" ht="15.75" customHeight="1" s="7"/>
-    <row r="83" ht="15.75" customHeight="1" s="7"/>
-    <row r="84" ht="15.75" customHeight="1" s="7"/>
-    <row r="85" ht="15.75" customHeight="1" s="7"/>
-    <row r="86" ht="15.75" customHeight="1" s="7"/>
-    <row r="87" ht="15.75" customHeight="1" s="7"/>
-    <row r="88" ht="15.75" customHeight="1" s="7"/>
-    <row r="89" ht="15.75" customHeight="1" s="7"/>
-    <row r="90" ht="15.75" customHeight="1" s="7"/>
-    <row r="91" ht="15.75" customHeight="1" s="7"/>
-    <row r="92" ht="15.75" customHeight="1" s="7"/>
-    <row r="93" ht="15.75" customHeight="1" s="7"/>
-    <row r="94" ht="15.75" customHeight="1" s="7"/>
-    <row r="95" ht="15.75" customHeight="1" s="7"/>
-    <row r="96" ht="15.75" customHeight="1" s="7"/>
-    <row r="97" ht="15.75" customHeight="1" s="7"/>
-    <row r="98" ht="15.75" customHeight="1" s="7"/>
-    <row r="99" ht="15.75" customHeight="1" s="7"/>
-    <row r="100" ht="15.75" customHeight="1" s="7"/>
-    <row r="101" ht="15.75" customHeight="1" s="7"/>
-    <row r="102" ht="15.75" customHeight="1" s="7"/>
-    <row r="103" ht="15.75" customHeight="1" s="7"/>
-    <row r="104" ht="15.75" customHeight="1" s="7"/>
-    <row r="105" ht="15.75" customHeight="1" s="7"/>
-    <row r="106" ht="15.75" customHeight="1" s="7"/>
-    <row r="107" ht="15.75" customHeight="1" s="7"/>
-    <row r="108" ht="15.75" customHeight="1" s="7"/>
-    <row r="109" ht="15.75" customHeight="1" s="7"/>
-    <row r="110" ht="15.75" customHeight="1" s="7"/>
-    <row r="111" ht="15.75" customHeight="1" s="7"/>
-    <row r="112" ht="15.75" customHeight="1" s="7"/>
-    <row r="113" ht="15.75" customHeight="1" s="7"/>
-    <row r="114" ht="15.75" customHeight="1" s="7"/>
-    <row r="115" ht="15.75" customHeight="1" s="7"/>
-    <row r="116" ht="15.75" customHeight="1" s="7"/>
-    <row r="117" ht="15.75" customHeight="1" s="7"/>
-    <row r="118" ht="15.75" customHeight="1" s="7"/>
-    <row r="119" ht="15.75" customHeight="1" s="7"/>
-    <row r="120" ht="15.75" customHeight="1" s="7"/>
-    <row r="121" ht="15.75" customHeight="1" s="7"/>
-    <row r="122" ht="15.75" customHeight="1" s="7"/>
-    <row r="123" ht="15.75" customHeight="1" s="7"/>
-    <row r="124" ht="15.75" customHeight="1" s="7"/>
-    <row r="125" ht="15.75" customHeight="1" s="7"/>
-    <row r="126" ht="15.75" customHeight="1" s="7"/>
-    <row r="127" ht="15.75" customHeight="1" s="7"/>
-    <row r="128" ht="15.75" customHeight="1" s="7"/>
-    <row r="129" ht="15.75" customHeight="1" s="7"/>
-    <row r="130" ht="15.75" customHeight="1" s="7"/>
-    <row r="131" ht="15.75" customHeight="1" s="7"/>
-    <row r="132" ht="15.75" customHeight="1" s="7"/>
-    <row r="133" ht="15.75" customHeight="1" s="7"/>
-    <row r="134" ht="15.75" customHeight="1" s="7"/>
-    <row r="135" ht="15.75" customHeight="1" s="7"/>
-    <row r="136" ht="15.75" customHeight="1" s="7"/>
-    <row r="137" ht="15.75" customHeight="1" s="7"/>
-    <row r="138" ht="15.75" customHeight="1" s="7"/>
-    <row r="139" ht="15.75" customHeight="1" s="7"/>
-    <row r="140" ht="15.75" customHeight="1" s="7"/>
-    <row r="141" ht="15.75" customHeight="1" s="7"/>
-    <row r="142" ht="15.75" customHeight="1" s="7"/>
-    <row r="143" ht="15.75" customHeight="1" s="7"/>
-    <row r="144" ht="15.75" customHeight="1" s="7"/>
-    <row r="145" ht="15.75" customHeight="1" s="7"/>
-    <row r="146" ht="15.75" customHeight="1" s="7"/>
-    <row r="147" ht="15.75" customHeight="1" s="7"/>
-    <row r="148" ht="15.75" customHeight="1" s="7"/>
-    <row r="149" ht="15.75" customHeight="1" s="7"/>
-    <row r="150" ht="15.75" customHeight="1" s="7"/>
-    <row r="151" ht="15.75" customHeight="1" s="7"/>
-    <row r="152" ht="15.75" customHeight="1" s="7"/>
-    <row r="153" ht="15.75" customHeight="1" s="7"/>
-    <row r="154" ht="15.75" customHeight="1" s="7"/>
-    <row r="155" ht="15.75" customHeight="1" s="7"/>
-    <row r="156" ht="15.75" customHeight="1" s="7"/>
-    <row r="157" ht="15.75" customHeight="1" s="7"/>
-    <row r="158" ht="15.75" customHeight="1" s="7"/>
-    <row r="159" ht="15.75" customHeight="1" s="7"/>
-    <row r="160" ht="15.75" customHeight="1" s="7"/>
-    <row r="161" ht="15.75" customHeight="1" s="7"/>
-    <row r="162" ht="15.75" customHeight="1" s="7"/>
-    <row r="163" ht="15.75" customHeight="1" s="7"/>
-    <row r="164" ht="15.75" customHeight="1" s="7"/>
-    <row r="165" ht="15.75" customHeight="1" s="7"/>
-    <row r="166" ht="15.75" customHeight="1" s="7"/>
-    <row r="167" ht="15.75" customHeight="1" s="7"/>
-    <row r="168" ht="15.75" customHeight="1" s="7"/>
-    <row r="169" ht="15.75" customHeight="1" s="7"/>
-    <row r="170" ht="15.75" customHeight="1" s="7"/>
-    <row r="171" ht="15.75" customHeight="1" s="7"/>
-    <row r="172" ht="15.75" customHeight="1" s="7"/>
-    <row r="173" ht="15.75" customHeight="1" s="7"/>
-    <row r="174" ht="15.75" customHeight="1" s="7"/>
-    <row r="175" ht="15.75" customHeight="1" s="7"/>
-    <row r="176" ht="15.75" customHeight="1" s="7"/>
-    <row r="177" ht="15.75" customHeight="1" s="7"/>
-    <row r="178" ht="15.75" customHeight="1" s="7"/>
-    <row r="179" ht="15.75" customHeight="1" s="7"/>
-    <row r="180" ht="15.75" customHeight="1" s="7"/>
-    <row r="181" ht="15.75" customHeight="1" s="7"/>
-    <row r="182" ht="15.75" customHeight="1" s="7"/>
-    <row r="183" ht="15.75" customHeight="1" s="7"/>
-    <row r="184" ht="15.75" customHeight="1" s="7"/>
-    <row r="185" ht="15.75" customHeight="1" s="7"/>
-    <row r="186" ht="15.75" customHeight="1" s="7"/>
-    <row r="187" ht="15.75" customHeight="1" s="7"/>
-    <row r="188" ht="15.75" customHeight="1" s="7"/>
-    <row r="189" ht="15.75" customHeight="1" s="7"/>
-    <row r="190" ht="15.75" customHeight="1" s="7"/>
-    <row r="191" ht="15.75" customHeight="1" s="7"/>
-    <row r="192" ht="15.75" customHeight="1" s="7"/>
-    <row r="193" ht="15.75" customHeight="1" s="7"/>
-    <row r="194" ht="15.75" customHeight="1" s="7"/>
-    <row r="195" ht="15.75" customHeight="1" s="7"/>
-    <row r="196" ht="15.75" customHeight="1" s="7"/>
-    <row r="197" ht="15.75" customHeight="1" s="7"/>
-    <row r="198" ht="15.75" customHeight="1" s="7"/>
-    <row r="199" ht="15.75" customHeight="1" s="7"/>
-    <row r="200" ht="15.75" customHeight="1" s="7"/>
-    <row r="201" ht="15.75" customHeight="1" s="7"/>
-    <row r="202" ht="15.75" customHeight="1" s="7"/>
-    <row r="203" ht="15.75" customHeight="1" s="7"/>
-    <row r="204" ht="15.75" customHeight="1" s="7"/>
-    <row r="205" ht="15.75" customHeight="1" s="7"/>
-    <row r="206" ht="15.75" customHeight="1" s="7"/>
-    <row r="207" ht="15.75" customHeight="1" s="7"/>
-    <row r="208" ht="15.75" customHeight="1" s="7"/>
-    <row r="209" ht="15.75" customHeight="1" s="7"/>
-    <row r="210" ht="15.75" customHeight="1" s="7"/>
-    <row r="211" ht="15.75" customHeight="1" s="7"/>
-    <row r="212" ht="15.75" customHeight="1" s="7"/>
-    <row r="213" ht="15.75" customHeight="1" s="7"/>
-    <row r="214" ht="15.75" customHeight="1" s="7"/>
-    <row r="215" ht="15.75" customHeight="1" s="7"/>
-    <row r="216" ht="15.75" customHeight="1" s="7"/>
-    <row r="217" ht="15.75" customHeight="1" s="7"/>
-    <row r="218" ht="15.75" customHeight="1" s="7"/>
-    <row r="219" ht="15.75" customHeight="1" s="7"/>
-    <row r="220" ht="15.75" customHeight="1" s="7"/>
-    <row r="221" ht="15.75" customHeight="1" s="7"/>
-    <row r="222" ht="15.75" customHeight="1" s="7"/>
-    <row r="223" ht="15.75" customHeight="1" s="7"/>
-    <row r="224" ht="15.75" customHeight="1" s="7"/>
-    <row r="225" ht="15.75" customHeight="1" s="7"/>
-    <row r="226" ht="15.75" customHeight="1" s="7"/>
-    <row r="227" ht="15.75" customHeight="1" s="7"/>
-    <row r="228" ht="15.75" customHeight="1" s="7"/>
-    <row r="229" ht="15.75" customHeight="1" s="7"/>
-    <row r="230" ht="15.75" customHeight="1" s="7"/>
-    <row r="231" ht="15.75" customHeight="1" s="7"/>
-    <row r="232" ht="15.75" customHeight="1" s="7"/>
-    <row r="233" ht="15.75" customHeight="1" s="7"/>
-    <row r="234" ht="15.75" customHeight="1" s="7"/>
-    <row r="235" ht="15.75" customHeight="1" s="7"/>
-    <row r="236" ht="15.75" customHeight="1" s="7"/>
-    <row r="237" ht="15.75" customHeight="1" s="7"/>
-    <row r="238" ht="15.75" customHeight="1" s="7"/>
-    <row r="239" ht="15.75" customHeight="1" s="7"/>
-    <row r="240" ht="15.75" customHeight="1" s="7"/>
-    <row r="241" ht="15.75" customHeight="1" s="7"/>
-    <row r="242" ht="15.75" customHeight="1" s="7"/>
-    <row r="243" ht="15.75" customHeight="1" s="7"/>
-    <row r="244" ht="15.75" customHeight="1" s="7"/>
-    <row r="245" ht="15.75" customHeight="1" s="7"/>
-    <row r="246" ht="15.75" customHeight="1" s="7"/>
-    <row r="247" ht="15.75" customHeight="1" s="7"/>
-    <row r="248" ht="15.75" customHeight="1" s="7"/>
-    <row r="249" ht="15.75" customHeight="1" s="7"/>
-    <row r="250" ht="15.75" customHeight="1" s="7"/>
-    <row r="251" ht="15.75" customHeight="1" s="7"/>
-    <row r="252" ht="15.75" customHeight="1" s="7"/>
-    <row r="253" ht="15.75" customHeight="1" s="7"/>
-    <row r="254" ht="15.75" customHeight="1" s="7"/>
-    <row r="255" ht="15.75" customHeight="1" s="7"/>
-    <row r="256" ht="15.75" customHeight="1" s="7"/>
-    <row r="257" ht="15.75" customHeight="1" s="7"/>
-    <row r="258" ht="15.75" customHeight="1" s="7"/>
-    <row r="259" ht="15.75" customHeight="1" s="7"/>
-    <row r="260" ht="15.75" customHeight="1" s="7"/>
-    <row r="261" ht="15.75" customHeight="1" s="7"/>
-    <row r="262" ht="15.75" customHeight="1" s="7"/>
-    <row r="263" ht="15.75" customHeight="1" s="7"/>
-    <row r="264" ht="15.75" customHeight="1" s="7"/>
-    <row r="265" ht="15.75" customHeight="1" s="7"/>
-    <row r="266" ht="15.75" customHeight="1" s="7"/>
-    <row r="267" ht="15.75" customHeight="1" s="7"/>
-    <row r="268" ht="15.75" customHeight="1" s="7"/>
-    <row r="269" ht="15.75" customHeight="1" s="7"/>
-    <row r="270" ht="15.75" customHeight="1" s="7"/>
-    <row r="271" ht="15.75" customHeight="1" s="7"/>
-    <row r="272" ht="15.75" customHeight="1" s="7"/>
-    <row r="273" ht="15.75" customHeight="1" s="7"/>
-    <row r="274" ht="15.75" customHeight="1" s="7"/>
-    <row r="275" ht="15.75" customHeight="1" s="7"/>
-    <row r="276" ht="15.75" customHeight="1" s="7"/>
-    <row r="277" ht="15.75" customHeight="1" s="7"/>
-    <row r="278" ht="15.75" customHeight="1" s="7"/>
-    <row r="279" ht="15.75" customHeight="1" s="7"/>
-    <row r="280" ht="15.75" customHeight="1" s="7"/>
-    <row r="281" ht="15.75" customHeight="1" s="7"/>
-    <row r="282" ht="15.75" customHeight="1" s="7"/>
-    <row r="283" ht="15.75" customHeight="1" s="7"/>
-    <row r="284" ht="15.75" customHeight="1" s="7"/>
-    <row r="285" ht="15.75" customHeight="1" s="7"/>
-    <row r="286" ht="15.75" customHeight="1" s="7"/>
-    <row r="287" ht="15.75" customHeight="1" s="7"/>
-    <row r="288" ht="15.75" customHeight="1" s="7"/>
-    <row r="289" ht="15.75" customHeight="1" s="7"/>
-    <row r="290" ht="15.75" customHeight="1" s="7"/>
-    <row r="291" ht="15.75" customHeight="1" s="7"/>
-    <row r="292" ht="15.75" customHeight="1" s="7"/>
-    <row r="293" ht="15.75" customHeight="1" s="7"/>
-    <row r="294" ht="15.75" customHeight="1" s="7"/>
-    <row r="295" ht="15.75" customHeight="1" s="7"/>
-    <row r="296" ht="15.75" customHeight="1" s="7"/>
-    <row r="297" ht="15.75" customHeight="1" s="7"/>
-    <row r="298" ht="15.75" customHeight="1" s="7"/>
-    <row r="299" ht="15.75" customHeight="1" s="7"/>
-    <row r="300" ht="15.75" customHeight="1" s="7"/>
-    <row r="301" ht="15.75" customHeight="1" s="7"/>
-    <row r="302" ht="15.75" customHeight="1" s="7"/>
-    <row r="303" ht="15.75" customHeight="1" s="7"/>
-    <row r="304" ht="15.75" customHeight="1" s="7"/>
-    <row r="305" ht="15.75" customHeight="1" s="7"/>
-    <row r="306" ht="15.75" customHeight="1" s="7"/>
-    <row r="307" ht="15.75" customHeight="1" s="7"/>
-    <row r="308" ht="15.75" customHeight="1" s="7"/>
-    <row r="309" ht="15.75" customHeight="1" s="7"/>
-    <row r="310" ht="15.75" customHeight="1" s="7"/>
-    <row r="311" ht="15.75" customHeight="1" s="7"/>
-    <row r="312" ht="15.75" customHeight="1" s="7"/>
-    <row r="313" ht="15.75" customHeight="1" s="7"/>
-    <row r="314" ht="15.75" customHeight="1" s="7"/>
-    <row r="315" ht="15.75" customHeight="1" s="7"/>
-    <row r="316" ht="15.75" customHeight="1" s="7"/>
-    <row r="317" ht="15.75" customHeight="1" s="7"/>
-    <row r="318" ht="15.75" customHeight="1" s="7"/>
-    <row r="319" ht="15.75" customHeight="1" s="7"/>
-    <row r="320" ht="15.75" customHeight="1" s="7"/>
-    <row r="321" ht="15.75" customHeight="1" s="7"/>
-    <row r="322" ht="15.75" customHeight="1" s="7"/>
-    <row r="323" ht="15.75" customHeight="1" s="7"/>
-    <row r="324" ht="15.75" customHeight="1" s="7"/>
-    <row r="325" ht="15.75" customHeight="1" s="7"/>
-    <row r="326" ht="15.75" customHeight="1" s="7"/>
-    <row r="327" ht="15.75" customHeight="1" s="7"/>
-    <row r="328" ht="15.75" customHeight="1" s="7"/>
-    <row r="329" ht="15.75" customHeight="1" s="7"/>
-    <row r="330" ht="15.75" customHeight="1" s="7"/>
-    <row r="331" ht="15.75" customHeight="1" s="7"/>
-    <row r="332" ht="15.75" customHeight="1" s="7"/>
-    <row r="333" ht="15.75" customHeight="1" s="7"/>
-    <row r="334" ht="15.75" customHeight="1" s="7"/>
-    <row r="335" ht="15.75" customHeight="1" s="7"/>
-    <row r="336" ht="15.75" customHeight="1" s="7"/>
-    <row r="337" ht="15.75" customHeight="1" s="7"/>
-    <row r="338" ht="15.75" customHeight="1" s="7"/>
-    <row r="339" ht="15.75" customHeight="1" s="7"/>
-    <row r="340" ht="15.75" customHeight="1" s="7"/>
-    <row r="341" ht="15.75" customHeight="1" s="7"/>
-    <row r="342" ht="15.75" customHeight="1" s="7"/>
-    <row r="343" ht="15.75" customHeight="1" s="7"/>
-    <row r="344" ht="15.75" customHeight="1" s="7"/>
-    <row r="345" ht="15.75" customHeight="1" s="7"/>
-    <row r="346" ht="15.75" customHeight="1" s="7"/>
-    <row r="347" ht="15.75" customHeight="1" s="7"/>
-    <row r="348" ht="15.75" customHeight="1" s="7"/>
-    <row r="349" ht="15.75" customHeight="1" s="7"/>
-    <row r="350" ht="15.75" customHeight="1" s="7"/>
-    <row r="351" ht="15.75" customHeight="1" s="7"/>
-    <row r="352" ht="15.75" customHeight="1" s="7"/>
-    <row r="353" ht="15.75" customHeight="1" s="7"/>
-    <row r="354" ht="15.75" customHeight="1" s="7"/>
-    <row r="355" ht="15.75" customHeight="1" s="7"/>
-    <row r="356" ht="15.75" customHeight="1" s="7"/>
-    <row r="357" ht="15.75" customHeight="1" s="7"/>
-    <row r="358" ht="15.75" customHeight="1" s="7"/>
-    <row r="359" ht="15.75" customHeight="1" s="7"/>
-    <row r="360" ht="15.75" customHeight="1" s="7"/>
-    <row r="361" ht="15.75" customHeight="1" s="7"/>
-    <row r="362" ht="15.75" customHeight="1" s="7"/>
-    <row r="363" ht="15.75" customHeight="1" s="7"/>
-    <row r="364" ht="15.75" customHeight="1" s="7"/>
-    <row r="365" ht="15.75" customHeight="1" s="7"/>
-    <row r="366" ht="15.75" customHeight="1" s="7"/>
-    <row r="367" ht="15.75" customHeight="1" s="7"/>
-    <row r="368" ht="15.75" customHeight="1" s="7"/>
-    <row r="369" ht="15.75" customHeight="1" s="7"/>
-    <row r="370" ht="15.75" customHeight="1" s="7"/>
-    <row r="371" ht="15.75" customHeight="1" s="7"/>
-    <row r="372" ht="15.75" customHeight="1" s="7"/>
-    <row r="373" ht="15.75" customHeight="1" s="7"/>
-    <row r="374" ht="15.75" customHeight="1" s="7"/>
-    <row r="375" ht="15.75" customHeight="1" s="7"/>
-    <row r="376" ht="15.75" customHeight="1" s="7"/>
-    <row r="377" ht="15.75" customHeight="1" s="7"/>
-    <row r="378" ht="15.75" customHeight="1" s="7"/>
-    <row r="379" ht="15.75" customHeight="1" s="7"/>
-    <row r="380" ht="15.75" customHeight="1" s="7"/>
-    <row r="381" ht="15.75" customHeight="1" s="7"/>
-    <row r="382" ht="15.75" customHeight="1" s="7"/>
-    <row r="383" ht="15.75" customHeight="1" s="7"/>
-    <row r="384" ht="15.75" customHeight="1" s="7"/>
-    <row r="385" ht="15.75" customHeight="1" s="7"/>
-    <row r="386" ht="15.75" customHeight="1" s="7"/>
-    <row r="387" ht="15.75" customHeight="1" s="7"/>
-    <row r="388" ht="15.75" customHeight="1" s="7"/>
-    <row r="389" ht="15.75" customHeight="1" s="7"/>
-    <row r="390" ht="15.75" customHeight="1" s="7"/>
-    <row r="391" ht="15.75" customHeight="1" s="7"/>
-    <row r="392" ht="15.75" customHeight="1" s="7"/>
-    <row r="393" ht="15.75" customHeight="1" s="7"/>
-    <row r="394" ht="15.75" customHeight="1" s="7"/>
-    <row r="395" ht="15.75" customHeight="1" s="7"/>
-    <row r="396" ht="15.75" customHeight="1" s="7"/>
-    <row r="397" ht="15.75" customHeight="1" s="7"/>
-    <row r="398" ht="15.75" customHeight="1" s="7"/>
-    <row r="399" ht="15.75" customHeight="1" s="7"/>
-    <row r="400" ht="15.75" customHeight="1" s="7"/>
-    <row r="401" ht="15.75" customHeight="1" s="7"/>
-    <row r="402" ht="15.75" customHeight="1" s="7"/>
-    <row r="403" ht="15.75" customHeight="1" s="7"/>
-    <row r="404" ht="15.75" customHeight="1" s="7"/>
-    <row r="405" ht="15.75" customHeight="1" s="7"/>
-    <row r="406" ht="15.75" customHeight="1" s="7"/>
-    <row r="407" ht="15.75" customHeight="1" s="7"/>
-    <row r="408" ht="15.75" customHeight="1" s="7"/>
-    <row r="409" ht="15.75" customHeight="1" s="7"/>
-    <row r="410" ht="15.75" customHeight="1" s="7"/>
-    <row r="411" ht="15.75" customHeight="1" s="7"/>
-    <row r="412" ht="15.75" customHeight="1" s="7"/>
-    <row r="413" ht="15.75" customHeight="1" s="7"/>
-    <row r="414" ht="15.75" customHeight="1" s="7"/>
-    <row r="415" ht="15.75" customHeight="1" s="7"/>
-    <row r="416" ht="15.75" customHeight="1" s="7"/>
-    <row r="417" ht="15.75" customHeight="1" s="7"/>
-    <row r="418" ht="15.75" customHeight="1" s="7"/>
-    <row r="419" ht="15.75" customHeight="1" s="7"/>
-    <row r="420" ht="15.75" customHeight="1" s="7"/>
-    <row r="421" ht="15.75" customHeight="1" s="7"/>
-    <row r="422" ht="15.75" customHeight="1" s="7"/>
-    <row r="423" ht="15.75" customHeight="1" s="7"/>
-    <row r="424" ht="15.75" customHeight="1" s="7"/>
-    <row r="425" ht="15.75" customHeight="1" s="7"/>
-    <row r="426" ht="15.75" customHeight="1" s="7"/>
-    <row r="427" ht="15.75" customHeight="1" s="7"/>
-    <row r="428" ht="15.75" customHeight="1" s="7"/>
-    <row r="429" ht="15.75" customHeight="1" s="7"/>
-    <row r="430" ht="15.75" customHeight="1" s="7"/>
-    <row r="431" ht="15.75" customHeight="1" s="7"/>
-    <row r="432" ht="15.75" customHeight="1" s="7"/>
-    <row r="433" ht="15.75" customHeight="1" s="7"/>
-    <row r="434" ht="15.75" customHeight="1" s="7"/>
-    <row r="435" ht="15.75" customHeight="1" s="7"/>
-    <row r="436" ht="15.75" customHeight="1" s="7"/>
-    <row r="437" ht="15.75" customHeight="1" s="7"/>
-    <row r="438" ht="15.75" customHeight="1" s="7"/>
-    <row r="439" ht="15.75" customHeight="1" s="7"/>
-    <row r="440" ht="15.75" customHeight="1" s="7"/>
-    <row r="441" ht="15.75" customHeight="1" s="7"/>
-    <row r="442" ht="15.75" customHeight="1" s="7"/>
-    <row r="443" ht="15.75" customHeight="1" s="7"/>
-    <row r="444" ht="15.75" customHeight="1" s="7"/>
-    <row r="445" ht="15.75" customHeight="1" s="7"/>
-    <row r="446" ht="15.75" customHeight="1" s="7"/>
-    <row r="447" ht="15.75" customHeight="1" s="7"/>
-    <row r="448" ht="15.75" customHeight="1" s="7"/>
-    <row r="449" ht="15.75" customHeight="1" s="7"/>
-    <row r="450" ht="15.75" customHeight="1" s="7"/>
-    <row r="451" ht="15.75" customHeight="1" s="7"/>
-    <row r="452" ht="15.75" customHeight="1" s="7"/>
-    <row r="453" ht="15.75" customHeight="1" s="7"/>
-    <row r="454" ht="15.75" customHeight="1" s="7"/>
-    <row r="455" ht="15.75" customHeight="1" s="7"/>
-    <row r="456" ht="15.75" customHeight="1" s="7"/>
-    <row r="457" ht="15.75" customHeight="1" s="7"/>
-    <row r="458" ht="15.75" customHeight="1" s="7"/>
-    <row r="459" ht="15.75" customHeight="1" s="7"/>
-    <row r="460" ht="15.75" customHeight="1" s="7"/>
-    <row r="461" ht="15.75" customHeight="1" s="7"/>
-    <row r="462" ht="15.75" customHeight="1" s="7"/>
-    <row r="463" ht="15.75" customHeight="1" s="7"/>
-    <row r="464" ht="15.75" customHeight="1" s="7"/>
-    <row r="465" ht="15.75" customHeight="1" s="7"/>
-    <row r="466" ht="15.75" customHeight="1" s="7"/>
-    <row r="467" ht="15.75" customHeight="1" s="7"/>
-    <row r="468" ht="15.75" customHeight="1" s="7"/>
-    <row r="469" ht="15.75" customHeight="1" s="7"/>
-    <row r="470" ht="15.75" customHeight="1" s="7"/>
-    <row r="471" ht="15.75" customHeight="1" s="7"/>
-    <row r="472" ht="15.75" customHeight="1" s="7"/>
-    <row r="473" ht="15.75" customHeight="1" s="7"/>
-    <row r="474" ht="15.75" customHeight="1" s="7"/>
-    <row r="475" ht="15.75" customHeight="1" s="7"/>
-    <row r="476" ht="15.75" customHeight="1" s="7"/>
-    <row r="477" ht="15.75" customHeight="1" s="7"/>
-    <row r="478" ht="15.75" customHeight="1" s="7"/>
-    <row r="479" ht="15.75" customHeight="1" s="7"/>
-    <row r="480" ht="15.75" customHeight="1" s="7"/>
-    <row r="481" ht="15.75" customHeight="1" s="7"/>
-    <row r="482" ht="15.75" customHeight="1" s="7"/>
-    <row r="483" ht="15.75" customHeight="1" s="7"/>
-    <row r="484" ht="15.75" customHeight="1" s="7"/>
-    <row r="485" ht="15.75" customHeight="1" s="7"/>
-    <row r="486" ht="15.75" customHeight="1" s="7"/>
-    <row r="487" ht="15.75" customHeight="1" s="7"/>
-    <row r="488" ht="15.75" customHeight="1" s="7"/>
-    <row r="489" ht="15.75" customHeight="1" s="7"/>
-    <row r="490" ht="15.75" customHeight="1" s="7"/>
-    <row r="491" ht="15.75" customHeight="1" s="7"/>
-    <row r="492" ht="15.75" customHeight="1" s="7"/>
-    <row r="493" ht="15.75" customHeight="1" s="7"/>
-    <row r="494" ht="15.75" customHeight="1" s="7"/>
-    <row r="495" ht="15.75" customHeight="1" s="7"/>
-    <row r="496" ht="15.75" customHeight="1" s="7"/>
-    <row r="497" ht="15.75" customHeight="1" s="7"/>
-    <row r="498" ht="15.75" customHeight="1" s="7"/>
-    <row r="499" ht="15.75" customHeight="1" s="7"/>
-    <row r="500" ht="15.75" customHeight="1" s="7"/>
-    <row r="501" ht="15.75" customHeight="1" s="7"/>
-    <row r="502" ht="15.75" customHeight="1" s="7"/>
-    <row r="503" ht="15.75" customHeight="1" s="7"/>
-    <row r="504" ht="15.75" customHeight="1" s="7"/>
-    <row r="505" ht="15.75" customHeight="1" s="7"/>
-    <row r="506" ht="15.75" customHeight="1" s="7"/>
-    <row r="507" ht="15.75" customHeight="1" s="7"/>
-    <row r="508" ht="15.75" customHeight="1" s="7"/>
-    <row r="509" ht="15.75" customHeight="1" s="7"/>
-    <row r="510" ht="15.75" customHeight="1" s="7"/>
-    <row r="511" ht="15.75" customHeight="1" s="7"/>
-    <row r="512" ht="15.75" customHeight="1" s="7"/>
-    <row r="513" ht="15.75" customHeight="1" s="7"/>
-    <row r="514" ht="15.75" customHeight="1" s="7"/>
-    <row r="515" ht="15.75" customHeight="1" s="7"/>
-    <row r="516" ht="15.75" customHeight="1" s="7"/>
-    <row r="517" ht="15.75" customHeight="1" s="7"/>
-    <row r="518" ht="15.75" customHeight="1" s="7"/>
-    <row r="519" ht="15.75" customHeight="1" s="7"/>
-    <row r="520" ht="15.75" customHeight="1" s="7"/>
-    <row r="521" ht="15.75" customHeight="1" s="7"/>
-    <row r="522" ht="15.75" customHeight="1" s="7"/>
-    <row r="523" ht="15.75" customHeight="1" s="7"/>
-    <row r="524" ht="15.75" customHeight="1" s="7"/>
-    <row r="525" ht="15.75" customHeight="1" s="7"/>
-    <row r="526" ht="15.75" customHeight="1" s="7"/>
-    <row r="527" ht="15.75" customHeight="1" s="7"/>
-    <row r="528" ht="15.75" customHeight="1" s="7"/>
-    <row r="529" ht="15.75" customHeight="1" s="7"/>
-    <row r="530" ht="15.75" customHeight="1" s="7"/>
-    <row r="531" ht="15.75" customHeight="1" s="7"/>
-    <row r="532" ht="15.75" customHeight="1" s="7"/>
-    <row r="533" ht="15.75" customHeight="1" s="7"/>
-    <row r="534" ht="15.75" customHeight="1" s="7"/>
-    <row r="535" ht="15.75" customHeight="1" s="7"/>
-    <row r="536" ht="15.75" customHeight="1" s="7"/>
-    <row r="537" ht="15.75" customHeight="1" s="7"/>
-    <row r="538" ht="15.75" customHeight="1" s="7"/>
-    <row r="539" ht="15.75" customHeight="1" s="7"/>
-    <row r="540" ht="15.75" customHeight="1" s="7"/>
-    <row r="541" ht="15.75" customHeight="1" s="7"/>
-    <row r="542" ht="15.75" customHeight="1" s="7"/>
-    <row r="543" ht="15.75" customHeight="1" s="7"/>
-    <row r="544" ht="15.75" customHeight="1" s="7"/>
-    <row r="545" ht="15.75" customHeight="1" s="7"/>
-    <row r="546" ht="15.75" customHeight="1" s="7"/>
-    <row r="547" ht="15.75" customHeight="1" s="7"/>
-    <row r="548" ht="15.75" customHeight="1" s="7"/>
-    <row r="549" ht="15.75" customHeight="1" s="7"/>
-    <row r="550" ht="15.75" customHeight="1" s="7"/>
-    <row r="551" ht="15.75" customHeight="1" s="7"/>
-    <row r="552" ht="15.75" customHeight="1" s="7"/>
-    <row r="553" ht="15.75" customHeight="1" s="7"/>
-    <row r="554" ht="15.75" customHeight="1" s="7"/>
-    <row r="555" ht="15.75" customHeight="1" s="7"/>
-    <row r="556" ht="15.75" customHeight="1" s="7"/>
-    <row r="557" ht="15.75" customHeight="1" s="7"/>
-    <row r="558" ht="15.75" customHeight="1" s="7"/>
-    <row r="559" ht="15.75" customHeight="1" s="7"/>
-    <row r="560" ht="15.75" customHeight="1" s="7"/>
-    <row r="561" ht="15.75" customHeight="1" s="7"/>
-    <row r="562" ht="15.75" customHeight="1" s="7"/>
-    <row r="563" ht="15.75" customHeight="1" s="7"/>
-    <row r="564" ht="15.75" customHeight="1" s="7"/>
-    <row r="565" ht="15.75" customHeight="1" s="7"/>
-    <row r="566" ht="15.75" customHeight="1" s="7"/>
-    <row r="567" ht="15.75" customHeight="1" s="7"/>
-    <row r="568" ht="15.75" customHeight="1" s="7"/>
-    <row r="569" ht="15.75" customHeight="1" s="7"/>
-    <row r="570" ht="15.75" customHeight="1" s="7"/>
-    <row r="571" ht="15.75" customHeight="1" s="7"/>
-    <row r="572" ht="15.75" customHeight="1" s="7"/>
-    <row r="573" ht="15.75" customHeight="1" s="7"/>
-    <row r="574" ht="15.75" customHeight="1" s="7"/>
-    <row r="575" ht="15.75" customHeight="1" s="7"/>
-    <row r="576" ht="15.75" customHeight="1" s="7"/>
-    <row r="577" ht="15.75" customHeight="1" s="7"/>
-    <row r="578" ht="15.75" customHeight="1" s="7"/>
-    <row r="579" ht="15.75" customHeight="1" s="7"/>
-    <row r="580" ht="15.75" customHeight="1" s="7"/>
-    <row r="581" ht="15.75" customHeight="1" s="7"/>
-    <row r="582" ht="15.75" customHeight="1" s="7"/>
-    <row r="583" ht="15.75" customHeight="1" s="7"/>
-    <row r="584" ht="15.75" customHeight="1" s="7"/>
-    <row r="585" ht="15.75" customHeight="1" s="7"/>
-    <row r="586" ht="15.75" customHeight="1" s="7"/>
-    <row r="587" ht="15.75" customHeight="1" s="7"/>
-    <row r="588" ht="15.75" customHeight="1" s="7"/>
-    <row r="589" ht="15.75" customHeight="1" s="7"/>
-    <row r="590" ht="15.75" customHeight="1" s="7"/>
-    <row r="591" ht="15.75" customHeight="1" s="7"/>
-    <row r="592" ht="15.75" customHeight="1" s="7"/>
-    <row r="593" ht="15.75" customHeight="1" s="7"/>
-    <row r="594" ht="15.75" customHeight="1" s="7"/>
-    <row r="595" ht="15.75" customHeight="1" s="7"/>
-    <row r="596" ht="15.75" customHeight="1" s="7"/>
-    <row r="597" ht="15.75" customHeight="1" s="7"/>
-    <row r="598" ht="15.75" customHeight="1" s="7"/>
-    <row r="599" ht="15.75" customHeight="1" s="7"/>
-    <row r="600" ht="15.75" customHeight="1" s="7"/>
-    <row r="601" ht="15.75" customHeight="1" s="7"/>
-    <row r="602" ht="15.75" customHeight="1" s="7"/>
-    <row r="603" ht="15.75" customHeight="1" s="7"/>
-    <row r="604" ht="15.75" customHeight="1" s="7"/>
-    <row r="605" ht="15.75" customHeight="1" s="7"/>
-    <row r="606" ht="15.75" customHeight="1" s="7"/>
-    <row r="607" ht="15.75" customHeight="1" s="7"/>
-    <row r="608" ht="15.75" customHeight="1" s="7"/>
-    <row r="609" ht="15.75" customHeight="1" s="7"/>
-    <row r="610" ht="15.75" customHeight="1" s="7"/>
-    <row r="611" ht="15.75" customHeight="1" s="7"/>
-    <row r="612" ht="15.75" customHeight="1" s="7"/>
-    <row r="613" ht="15.75" customHeight="1" s="7"/>
-    <row r="614" ht="15.75" customHeight="1" s="7"/>
-    <row r="615" ht="15.75" customHeight="1" s="7"/>
-    <row r="616" ht="15.75" customHeight="1" s="7"/>
-    <row r="617" ht="15.75" customHeight="1" s="7"/>
-    <row r="618" ht="15.75" customHeight="1" s="7"/>
-    <row r="619" ht="15.75" customHeight="1" s="7"/>
-    <row r="620" ht="15.75" customHeight="1" s="7"/>
-    <row r="621" ht="15.75" customHeight="1" s="7"/>
-    <row r="622" ht="15.75" customHeight="1" s="7"/>
-    <row r="623" ht="15.75" customHeight="1" s="7"/>
-    <row r="624" ht="15.75" customHeight="1" s="7"/>
-    <row r="625" ht="15.75" customHeight="1" s="7"/>
-    <row r="626" ht="15.75" customHeight="1" s="7"/>
-    <row r="627" ht="15.75" customHeight="1" s="7"/>
-    <row r="628" ht="15.75" customHeight="1" s="7"/>
-    <row r="629" ht="15.75" customHeight="1" s="7"/>
-    <row r="630" ht="15.75" customHeight="1" s="7"/>
-    <row r="631" ht="15.75" customHeight="1" s="7"/>
-    <row r="632" ht="15.75" customHeight="1" s="7"/>
-    <row r="633" ht="15.75" customHeight="1" s="7"/>
-    <row r="634" ht="15.75" customHeight="1" s="7"/>
-    <row r="635" ht="15.75" customHeight="1" s="7"/>
-    <row r="636" ht="15.75" customHeight="1" s="7"/>
-    <row r="637" ht="15.75" customHeight="1" s="7"/>
-    <row r="638" ht="15.75" customHeight="1" s="7"/>
-    <row r="639" ht="15.75" customHeight="1" s="7"/>
-    <row r="640" ht="15.75" customHeight="1" s="7"/>
-    <row r="641" ht="15.75" customHeight="1" s="7"/>
-    <row r="642" ht="15.75" customHeight="1" s="7"/>
-    <row r="643" ht="15.75" customHeight="1" s="7"/>
-    <row r="644" ht="15.75" customHeight="1" s="7"/>
-    <row r="645" ht="15.75" customHeight="1" s="7"/>
-    <row r="646" ht="15.75" customHeight="1" s="7"/>
-    <row r="647" ht="15.75" customHeight="1" s="7"/>
-    <row r="648" ht="15.75" customHeight="1" s="7"/>
-    <row r="649" ht="15.75" customHeight="1" s="7"/>
-    <row r="650" ht="15.75" customHeight="1" s="7"/>
-    <row r="651" ht="15.75" customHeight="1" s="7"/>
-    <row r="652" ht="15.75" customHeight="1" s="7"/>
-    <row r="653" ht="15.75" customHeight="1" s="7"/>
-    <row r="654" ht="15.75" customHeight="1" s="7"/>
-    <row r="655" ht="15.75" customHeight="1" s="7"/>
-    <row r="656" ht="15.75" customHeight="1" s="7"/>
-    <row r="657" ht="15.75" customHeight="1" s="7"/>
-    <row r="658" ht="15.75" customHeight="1" s="7"/>
-    <row r="659" ht="15.75" customHeight="1" s="7"/>
-    <row r="660" ht="15.75" customHeight="1" s="7"/>
-    <row r="661" ht="15.75" customHeight="1" s="7"/>
-    <row r="662" ht="15.75" customHeight="1" s="7"/>
-    <row r="663" ht="15.75" customHeight="1" s="7"/>
-    <row r="664" ht="15.75" customHeight="1" s="7"/>
-    <row r="665" ht="15.75" customHeight="1" s="7"/>
-    <row r="666" ht="15.75" customHeight="1" s="7"/>
-    <row r="667" ht="15.75" customHeight="1" s="7"/>
-    <row r="668" ht="15.75" customHeight="1" s="7"/>
-    <row r="669" ht="15.75" customHeight="1" s="7"/>
-    <row r="670" ht="15.75" customHeight="1" s="7"/>
-    <row r="671" ht="15.75" customHeight="1" s="7"/>
-    <row r="672" ht="15.75" customHeight="1" s="7"/>
-    <row r="673" ht="15.75" customHeight="1" s="7"/>
-    <row r="674" ht="15.75" customHeight="1" s="7"/>
-    <row r="675" ht="15.75" customHeight="1" s="7"/>
-    <row r="676" ht="15.75" customHeight="1" s="7"/>
-    <row r="677" ht="15.75" customHeight="1" s="7"/>
-    <row r="678" ht="15.75" customHeight="1" s="7"/>
-    <row r="679" ht="15.75" customHeight="1" s="7"/>
-    <row r="680" ht="15.75" customHeight="1" s="7"/>
-    <row r="681" ht="15.75" customHeight="1" s="7"/>
-    <row r="682" ht="15.75" customHeight="1" s="7"/>
-    <row r="683" ht="15.75" customHeight="1" s="7"/>
-    <row r="684" ht="15.75" customHeight="1" s="7"/>
-    <row r="685" ht="15.75" customHeight="1" s="7"/>
-    <row r="686" ht="15.75" customHeight="1" s="7"/>
-    <row r="687" ht="15.75" customHeight="1" s="7"/>
-    <row r="688" ht="15.75" customHeight="1" s="7"/>
-    <row r="689" ht="15.75" customHeight="1" s="7"/>
-    <row r="690" ht="15.75" customHeight="1" s="7"/>
-    <row r="691" ht="15.75" customHeight="1" s="7"/>
-    <row r="692" ht="15.75" customHeight="1" s="7"/>
-    <row r="693" ht="15.75" customHeight="1" s="7"/>
-    <row r="694" ht="15.75" customHeight="1" s="7"/>
-    <row r="695" ht="15.75" customHeight="1" s="7"/>
-    <row r="696" ht="15.75" customHeight="1" s="7"/>
-    <row r="697" ht="15.75" customHeight="1" s="7"/>
-    <row r="698" ht="15.75" customHeight="1" s="7"/>
-    <row r="699" ht="15.75" customHeight="1" s="7"/>
-    <row r="700" ht="15.75" customHeight="1" s="7"/>
-    <row r="701" ht="15.75" customHeight="1" s="7"/>
-    <row r="702" ht="15.75" customHeight="1" s="7"/>
-    <row r="703" ht="15.75" customHeight="1" s="7"/>
-    <row r="704" ht="15.75" customHeight="1" s="7"/>
-    <row r="705" ht="15.75" customHeight="1" s="7"/>
-    <row r="706" ht="15.75" customHeight="1" s="7"/>
-    <row r="707" ht="15.75" customHeight="1" s="7"/>
-    <row r="708" ht="15.75" customHeight="1" s="7"/>
-    <row r="709" ht="15.75" customHeight="1" s="7"/>
-    <row r="710" ht="15.75" customHeight="1" s="7"/>
-    <row r="711" ht="15.75" customHeight="1" s="7"/>
-    <row r="712" ht="15.75" customHeight="1" s="7"/>
-    <row r="713" ht="15.75" customHeight="1" s="7"/>
-    <row r="714" ht="15.75" customHeight="1" s="7"/>
-    <row r="715" ht="15.75" customHeight="1" s="7"/>
-    <row r="716" ht="15.75" customHeight="1" s="7"/>
-    <row r="717" ht="15.75" customHeight="1" s="7"/>
-    <row r="718" ht="15.75" customHeight="1" s="7"/>
-    <row r="719" ht="15.75" customHeight="1" s="7"/>
-    <row r="720" ht="15.75" customHeight="1" s="7"/>
-    <row r="721" ht="15.75" customHeight="1" s="7"/>
-    <row r="722" ht="15.75" customHeight="1" s="7"/>
-    <row r="723" ht="15.75" customHeight="1" s="7"/>
-    <row r="724" ht="15.75" customHeight="1" s="7"/>
-    <row r="725" ht="15.75" customHeight="1" s="7"/>
-    <row r="726" ht="15.75" customHeight="1" s="7"/>
-    <row r="727" ht="15.75" customHeight="1" s="7"/>
-    <row r="728" ht="15.75" customHeight="1" s="7"/>
-    <row r="729" ht="15.75" customHeight="1" s="7"/>
-    <row r="730" ht="15.75" customHeight="1" s="7"/>
-    <row r="731" ht="15.75" customHeight="1" s="7"/>
-    <row r="732" ht="15.75" customHeight="1" s="7"/>
-    <row r="733" ht="15.75" customHeight="1" s="7"/>
-    <row r="734" ht="15.75" customHeight="1" s="7"/>
-    <row r="735" ht="15.75" customHeight="1" s="7"/>
-    <row r="736" ht="15.75" customHeight="1" s="7"/>
-    <row r="737" ht="15.75" customHeight="1" s="7"/>
-    <row r="738" ht="15.75" customHeight="1" s="7"/>
-    <row r="739" ht="15.75" customHeight="1" s="7"/>
-    <row r="740" ht="15.75" customHeight="1" s="7"/>
-    <row r="741" ht="15.75" customHeight="1" s="7"/>
-    <row r="742" ht="15.75" customHeight="1" s="7"/>
-    <row r="743" ht="15.75" customHeight="1" s="7"/>
-    <row r="744" ht="15.75" customHeight="1" s="7"/>
-    <row r="745" ht="15.75" customHeight="1" s="7"/>
-    <row r="746" ht="15.75" customHeight="1" s="7"/>
-    <row r="747" ht="15.75" customHeight="1" s="7"/>
-    <row r="748" ht="15.75" customHeight="1" s="7"/>
-    <row r="749" ht="15.75" customHeight="1" s="7"/>
-    <row r="750" ht="15.75" customHeight="1" s="7"/>
-    <row r="751" ht="15.75" customHeight="1" s="7"/>
-    <row r="752" ht="15.75" customHeight="1" s="7"/>
-    <row r="753" ht="15.75" customHeight="1" s="7"/>
-    <row r="754" ht="15.75" customHeight="1" s="7"/>
-    <row r="755" ht="15.75" customHeight="1" s="7"/>
-    <row r="756" ht="15.75" customHeight="1" s="7"/>
-    <row r="757" ht="15.75" customHeight="1" s="7"/>
-    <row r="758" ht="15.75" customHeight="1" s="7"/>
-    <row r="759" ht="15.75" customHeight="1" s="7"/>
-    <row r="760" ht="15.75" customHeight="1" s="7"/>
-    <row r="761" ht="15.75" customHeight="1" s="7"/>
-    <row r="762" ht="15.75" customHeight="1" s="7"/>
-    <row r="763" ht="15.75" customHeight="1" s="7"/>
-    <row r="764" ht="15.75" customHeight="1" s="7"/>
-    <row r="765" ht="15.75" customHeight="1" s="7"/>
-    <row r="766" ht="15.75" customHeight="1" s="7"/>
-    <row r="767" ht="15.75" customHeight="1" s="7"/>
-    <row r="768" ht="15.75" customHeight="1" s="7"/>
-    <row r="769" ht="15.75" customHeight="1" s="7"/>
-    <row r="770" ht="15.75" customHeight="1" s="7"/>
-    <row r="771" ht="15.75" customHeight="1" s="7"/>
-    <row r="772" ht="15.75" customHeight="1" s="7"/>
-    <row r="773" ht="15.75" customHeight="1" s="7"/>
-    <row r="774" ht="15.75" customHeight="1" s="7"/>
-    <row r="775" ht="15.75" customHeight="1" s="7"/>
-    <row r="776" ht="15.75" customHeight="1" s="7"/>
-    <row r="777" ht="15.75" customHeight="1" s="7"/>
-    <row r="778" ht="15.75" customHeight="1" s="7"/>
-    <row r="779" ht="15.75" customHeight="1" s="7"/>
-    <row r="780" ht="15.75" customHeight="1" s="7"/>
-    <row r="781" ht="15.75" customHeight="1" s="7"/>
-    <row r="782" ht="15.75" customHeight="1" s="7"/>
-    <row r="783" ht="15.75" customHeight="1" s="7"/>
-    <row r="784" ht="15.75" customHeight="1" s="7"/>
-    <row r="785" ht="15.75" customHeight="1" s="7"/>
-    <row r="786" ht="15.75" customHeight="1" s="7"/>
-    <row r="787" ht="15.75" customHeight="1" s="7"/>
-    <row r="788" ht="15.75" customHeight="1" s="7"/>
-    <row r="789" ht="15.75" customHeight="1" s="7"/>
-    <row r="790" ht="15.75" customHeight="1" s="7"/>
-    <row r="791" ht="15.75" customHeight="1" s="7"/>
-    <row r="792" ht="15.75" customHeight="1" s="7"/>
-    <row r="793" ht="15.75" customHeight="1" s="7"/>
-    <row r="794" ht="15.75" customHeight="1" s="7"/>
-    <row r="795" ht="15.75" customHeight="1" s="7"/>
-    <row r="796" ht="15.75" customHeight="1" s="7"/>
-    <row r="797" ht="15.75" customHeight="1" s="7"/>
-    <row r="798" ht="15.75" customHeight="1" s="7"/>
-    <row r="799" ht="15.75" customHeight="1" s="7"/>
-    <row r="800" ht="15.75" customHeight="1" s="7"/>
-    <row r="801" ht="15.75" customHeight="1" s="7"/>
-    <row r="802" ht="15.75" customHeight="1" s="7"/>
-    <row r="803" ht="15.75" customHeight="1" s="7"/>
-    <row r="804" ht="15.75" customHeight="1" s="7"/>
-    <row r="805" ht="15.75" customHeight="1" s="7"/>
-    <row r="806" ht="15.75" customHeight="1" s="7"/>
-    <row r="807" ht="15.75" customHeight="1" s="7"/>
-    <row r="808" ht="15.75" customHeight="1" s="7"/>
-    <row r="809" ht="15.75" customHeight="1" s="7"/>
-    <row r="810" ht="15.75" customHeight="1" s="7"/>
-    <row r="811" ht="15.75" customHeight="1" s="7"/>
-    <row r="812" ht="15.75" customHeight="1" s="7"/>
-    <row r="813" ht="15.75" customHeight="1" s="7"/>
-    <row r="814" ht="15.75" customHeight="1" s="7"/>
-    <row r="815" ht="15.75" customHeight="1" s="7"/>
-    <row r="816" ht="15.75" customHeight="1" s="7"/>
-    <row r="817" ht="15.75" customHeight="1" s="7"/>
-    <row r="818" ht="15.75" customHeight="1" s="7"/>
-    <row r="819" ht="15.75" customHeight="1" s="7"/>
-    <row r="820" ht="15.75" customHeight="1" s="7"/>
-    <row r="821" ht="15.75" customHeight="1" s="7"/>
-    <row r="822" ht="15.75" customHeight="1" s="7"/>
-    <row r="823" ht="15.75" customHeight="1" s="7"/>
-    <row r="824" ht="15.75" customHeight="1" s="7"/>
-    <row r="825" ht="15.75" customHeight="1" s="7"/>
-    <row r="826" ht="15.75" customHeight="1" s="7"/>
-    <row r="827" ht="15.75" customHeight="1" s="7"/>
-    <row r="828" ht="15.75" customHeight="1" s="7"/>
-    <row r="829" ht="15.75" customHeight="1" s="7"/>
-    <row r="830" ht="15.75" customHeight="1" s="7"/>
-    <row r="831" ht="15.75" customHeight="1" s="7"/>
-    <row r="832" ht="15.75" customHeight="1" s="7"/>
-    <row r="833" ht="15.75" customHeight="1" s="7"/>
-    <row r="834" ht="15.75" customHeight="1" s="7"/>
-    <row r="835" ht="15.75" customHeight="1" s="7"/>
-    <row r="836" ht="15.75" customHeight="1" s="7"/>
-    <row r="837" ht="15.75" customHeight="1" s="7"/>
-    <row r="838" ht="15.75" customHeight="1" s="7"/>
-    <row r="839" ht="15.75" customHeight="1" s="7"/>
-    <row r="840" ht="15.75" customHeight="1" s="7"/>
-    <row r="841" ht="15.75" customHeight="1" s="7"/>
-    <row r="842" ht="15.75" customHeight="1" s="7"/>
-    <row r="843" ht="15.75" customHeight="1" s="7"/>
-    <row r="844" ht="15.75" customHeight="1" s="7"/>
-    <row r="845" ht="15.75" customHeight="1" s="7"/>
-    <row r="846" ht="15.75" customHeight="1" s="7"/>
-    <row r="847" ht="15.75" customHeight="1" s="7"/>
-    <row r="848" ht="15.75" customHeight="1" s="7"/>
-    <row r="849" ht="15.75" customHeight="1" s="7"/>
-    <row r="850" ht="15.75" customHeight="1" s="7"/>
-    <row r="851" ht="15.75" customHeight="1" s="7"/>
-    <row r="852" ht="15.75" customHeight="1" s="7"/>
-    <row r="853" ht="15.75" customHeight="1" s="7"/>
-    <row r="854" ht="15.75" customHeight="1" s="7"/>
-    <row r="855" ht="15.75" customHeight="1" s="7"/>
-    <row r="856" ht="15.75" customHeight="1" s="7"/>
-    <row r="857" ht="15.75" customHeight="1" s="7"/>
-    <row r="858" ht="15.75" customHeight="1" s="7"/>
-    <row r="859" ht="15.75" customHeight="1" s="7"/>
-    <row r="860" ht="15.75" customHeight="1" s="7"/>
-    <row r="861" ht="15.75" customHeight="1" s="7"/>
-    <row r="862" ht="15.75" customHeight="1" s="7"/>
-    <row r="863" ht="15.75" customHeight="1" s="7"/>
-    <row r="864" ht="15.75" customHeight="1" s="7"/>
-    <row r="865" ht="15.75" customHeight="1" s="7"/>
-    <row r="866" ht="15.75" customHeight="1" s="7"/>
-    <row r="867" ht="15.75" customHeight="1" s="7"/>
-    <row r="868" ht="15.75" customHeight="1" s="7"/>
-    <row r="869" ht="15.75" customHeight="1" s="7"/>
-    <row r="870" ht="15.75" customHeight="1" s="7"/>
-    <row r="871" ht="15.75" customHeight="1" s="7"/>
-    <row r="872" ht="15.75" customHeight="1" s="7"/>
-    <row r="873" ht="15.75" customHeight="1" s="7"/>
-    <row r="874" ht="15.75" customHeight="1" s="7"/>
-    <row r="875" ht="15.75" customHeight="1" s="7"/>
-    <row r="876" ht="15.75" customHeight="1" s="7"/>
-    <row r="877" ht="15.75" customHeight="1" s="7"/>
-    <row r="878" ht="15.75" customHeight="1" s="7"/>
-    <row r="879" ht="15.75" customHeight="1" s="7"/>
-    <row r="880" ht="15.75" customHeight="1" s="7"/>
-    <row r="881" ht="15.75" customHeight="1" s="7"/>
-    <row r="882" ht="15.75" customHeight="1" s="7"/>
-    <row r="883" ht="15.75" customHeight="1" s="7"/>
-    <row r="884" ht="15.75" customHeight="1" s="7"/>
-    <row r="885" ht="15.75" customHeight="1" s="7"/>
-    <row r="886" ht="15.75" customHeight="1" s="7"/>
-    <row r="887" ht="15.75" customHeight="1" s="7"/>
-    <row r="888" ht="15.75" customHeight="1" s="7"/>
-    <row r="889" ht="15.75" customHeight="1" s="7"/>
-    <row r="890" ht="15.75" customHeight="1" s="7"/>
-    <row r="891" ht="15.75" customHeight="1" s="7"/>
-    <row r="892" ht="15.75" customHeight="1" s="7"/>
-    <row r="893" ht="15.75" customHeight="1" s="7"/>
-    <row r="894" ht="15.75" customHeight="1" s="7"/>
-    <row r="895" ht="15.75" customHeight="1" s="7"/>
-    <row r="896" ht="15.75" customHeight="1" s="7"/>
-    <row r="897" ht="15.75" customHeight="1" s="7"/>
-    <row r="898" ht="15.75" customHeight="1" s="7"/>
-    <row r="899" ht="15.75" customHeight="1" s="7"/>
-    <row r="900" ht="15.75" customHeight="1" s="7"/>
-    <row r="901" ht="15.75" customHeight="1" s="7"/>
-    <row r="902" ht="15.75" customHeight="1" s="7"/>
-    <row r="903" ht="15.75" customHeight="1" s="7"/>
-    <row r="904" ht="15.75" customHeight="1" s="7"/>
-    <row r="905" ht="15.75" customHeight="1" s="7"/>
-    <row r="906" ht="15.75" customHeight="1" s="7"/>
-    <row r="907" ht="15.75" customHeight="1" s="7"/>
-    <row r="908" ht="15.75" customHeight="1" s="7"/>
-    <row r="909" ht="15.75" customHeight="1" s="7"/>
-    <row r="910" ht="15.75" customHeight="1" s="7"/>
-    <row r="911" ht="15.75" customHeight="1" s="7"/>
-    <row r="912" ht="15.75" customHeight="1" s="7"/>
-    <row r="913" ht="15.75" customHeight="1" s="7"/>
-    <row r="914" ht="15.75" customHeight="1" s="7"/>
-    <row r="915" ht="15.75" customHeight="1" s="7"/>
-    <row r="916" ht="15.75" customHeight="1" s="7"/>
-    <row r="917" ht="15.75" customHeight="1" s="7"/>
-    <row r="918" ht="15.75" customHeight="1" s="7"/>
-    <row r="919" ht="15.75" customHeight="1" s="7"/>
-    <row r="920" ht="15.75" customHeight="1" s="7"/>
-    <row r="921" ht="15.75" customHeight="1" s="7"/>
-    <row r="922" ht="15.75" customHeight="1" s="7"/>
-    <row r="923" ht="15.75" customHeight="1" s="7"/>
-    <row r="924" ht="15.75" customHeight="1" s="7"/>
-    <row r="925" ht="15.75" customHeight="1" s="7"/>
-    <row r="926" ht="15.75" customHeight="1" s="7"/>
-    <row r="927" ht="15.75" customHeight="1" s="7"/>
-    <row r="928" ht="15.75" customHeight="1" s="7"/>
-    <row r="929" ht="15.75" customHeight="1" s="7"/>
-    <row r="930" ht="15.75" customHeight="1" s="7"/>
-    <row r="931" ht="15.75" customHeight="1" s="7"/>
-    <row r="932" ht="15.75" customHeight="1" s="7"/>
-    <row r="933" ht="15.75" customHeight="1" s="7"/>
-    <row r="934" ht="15.75" customHeight="1" s="7"/>
-    <row r="935" ht="15.75" customHeight="1" s="7"/>
-    <row r="936" ht="15.75" customHeight="1" s="7"/>
-    <row r="937" ht="15.75" customHeight="1" s="7"/>
-    <row r="938" ht="15.75" customHeight="1" s="7"/>
-    <row r="939" ht="15.75" customHeight="1" s="7"/>
-    <row r="940" ht="15.75" customHeight="1" s="7"/>
-    <row r="941" ht="15.75" customHeight="1" s="7"/>
-    <row r="942" ht="15.75" customHeight="1" s="7"/>
-    <row r="943" ht="15.75" customHeight="1" s="7"/>
-    <row r="944" ht="15.75" customHeight="1" s="7"/>
-    <row r="945" ht="15.75" customHeight="1" s="7"/>
-    <row r="946" ht="15.75" customHeight="1" s="7"/>
-    <row r="947" ht="15.75" customHeight="1" s="7"/>
-    <row r="948" ht="15.75" customHeight="1" s="7"/>
-    <row r="949" ht="15.75" customHeight="1" s="7"/>
-    <row r="950" ht="15.75" customHeight="1" s="7"/>
-    <row r="951" ht="15.75" customHeight="1" s="7"/>
-    <row r="952" ht="15.75" customHeight="1" s="7"/>
-    <row r="953" ht="15.75" customHeight="1" s="7"/>
-    <row r="954" ht="15.75" customHeight="1" s="7"/>
-    <row r="955" ht="15.75" customHeight="1" s="7"/>
-    <row r="956" ht="15.75" customHeight="1" s="7"/>
-    <row r="957" ht="15.75" customHeight="1" s="7"/>
-    <row r="958" ht="15.75" customHeight="1" s="7"/>
-    <row r="959" ht="15.75" customHeight="1" s="7"/>
-    <row r="960" ht="15.75" customHeight="1" s="7"/>
-    <row r="961" ht="15.75" customHeight="1" s="7"/>
-    <row r="962" ht="15.75" customHeight="1" s="7"/>
-    <row r="963" ht="15.75" customHeight="1" s="7"/>
-    <row r="964" ht="15.75" customHeight="1" s="7"/>
-    <row r="965" ht="15.75" customHeight="1" s="7"/>
-    <row r="966" ht="15.75" customHeight="1" s="7"/>
-    <row r="967" ht="15.75" customHeight="1" s="7"/>
-    <row r="968" ht="15.75" customHeight="1" s="7"/>
-    <row r="969" ht="15.75" customHeight="1" s="7"/>
-    <row r="970" ht="15.75" customHeight="1" s="7"/>
-    <row r="971" ht="15.75" customHeight="1" s="7"/>
-    <row r="972" ht="15.75" customHeight="1" s="7"/>
-    <row r="973" ht="15.75" customHeight="1" s="7"/>
-    <row r="974" ht="15.75" customHeight="1" s="7"/>
-    <row r="975" ht="15.75" customHeight="1" s="7"/>
-    <row r="976" ht="15.75" customHeight="1" s="7"/>
-    <row r="977" ht="15.75" customHeight="1" s="7"/>
-    <row r="978" ht="15.75" customHeight="1" s="7"/>
-    <row r="979" ht="15.75" customHeight="1" s="7"/>
-    <row r="980" ht="15.75" customHeight="1" s="7"/>
-    <row r="981" ht="15.75" customHeight="1" s="7"/>
-    <row r="982" ht="15.75" customHeight="1" s="7"/>
-    <row r="983" ht="15.75" customHeight="1" s="7"/>
-    <row r="984" ht="15.75" customHeight="1" s="7"/>
-    <row r="985" ht="15.75" customHeight="1" s="7"/>
-    <row r="986" ht="15.75" customHeight="1" s="7"/>
-    <row r="987" ht="15.75" customHeight="1" s="7"/>
-    <row r="988" ht="15.75" customHeight="1" s="7"/>
-    <row r="989" ht="15.75" customHeight="1" s="7"/>
-    <row r="990" ht="15.75" customHeight="1" s="7"/>
-    <row r="991" ht="15.75" customHeight="1" s="7"/>
-    <row r="992" ht="15.75" customHeight="1" s="7"/>
-    <row r="993" ht="15.75" customHeight="1" s="7"/>
-    <row r="994" ht="15.75" customHeight="1" s="7"/>
-    <row r="995" ht="15.75" customHeight="1" s="7"/>
-    <row r="996" ht="15.75" customHeight="1" s="7"/>
-    <row r="997" ht="15.75" customHeight="1" s="7"/>
-    <row r="998" ht="15.75" customHeight="1" s="7"/>
-    <row r="999" ht="15.75" customHeight="1" s="7"/>
-    <row r="1000" ht="15.75" customHeight="1" s="7"/>
   </sheetData>
-  <mergeCells count="28">
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="D27:D28"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="D17:D18"/>
-    <mergeCell ref="B24:B26"/>
-    <mergeCell ref="D24:D26"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="B11:B16"/>
-    <mergeCell ref="B2:B7"/>
-    <mergeCell ref="D11:D16"/>
-    <mergeCell ref="D2:D7"/>
-    <mergeCell ref="C31:C32"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="B19:B20"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="B21:B23"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="C11:C16"/>
-    <mergeCell ref="D21:D23"/>
-    <mergeCell ref="C2:C7"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="C19:C20"/>
-    <mergeCell ref="D19:D20"/>
-    <mergeCell ref="B31:B32"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
-  <pageSetup orientation="landscape"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Groups_Module/Groups_Module_Test_Cases.xlsx
+++ b/Groups_Module/Groups_Module_Test_Cases.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -698,227 +698,183 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="2" t="n"/>
+      <c r="B8" s="2" t="n"/>
+      <c r="C8" s="2" t="n"/>
+      <c r="D8" s="2" t="n"/>
+      <c r="E8" s="2" t="n"/>
+      <c r="F8" s="2" t="n"/>
+      <c r="G8" s="2" t="n"/>
+      <c r="H8" s="2" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>GROUPS_007</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>Verify Group List display</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>User is logged in, no groups exist</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Verify empty group list state</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Groups tab with no groups.
 2. Observe display.</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>Empty state message should display (e.g., "No groups found" or create group prompt).</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>GROUPS_008</t>
         </is>
       </c>
-      <c r="B9" s="2" t="n"/>
-      <c r="C9" s="2" t="n"/>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="B10" s="2" t="n"/>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>User is logged in, group has very long name</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Verify handling of very long group names</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Groups tab.
 2. Find group with very long name.
 3. Observe display.</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>Long names should be truncated with ellipsis (...) without breaking layout.</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Low / Medium</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="n"/>
+      <c r="B11" s="2" t="n"/>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" s="2" t="n"/>
+      <c r="E11" s="2" t="n"/>
+      <c r="F11" s="2" t="n"/>
+      <c r="G11" s="2" t="n"/>
+      <c r="H11" s="2" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>GROUPS_009</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>Verify Group List scrolling</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>User is logged in, multiple groups exist</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Verify group list scrolling functionality</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Groups tab.
 2. Scroll down through the list.
 3. Scroll back up.</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>List should scroll smoothly; group entries should remain properly formatted.</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>High / Medium</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>GROUPS_010</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>Verify Group Search</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>User is logged in and on Groups tab</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Verify search field is visible and accessible</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Groups tab.
 2. Observe search field at top.</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>Search field should be visible with placeholder text "Search".</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>GROUPS_011</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n"/>
-      <c r="C12" s="2" t="n"/>
-      <c r="D12" s="2" t="n"/>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Verify search by group name</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1. Navigate to Groups tab.
-2. Type "Hiking" in search field.
-3. Observe results.</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>"Hiking Group" should appear in filtered results.</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>GROUPS_012</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n"/>
-      <c r="C13" s="2" t="n"/>
-      <c r="D13" s="2" t="n"/>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Verify search by partial name</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>1. Navigate to Groups tab.
-2. Type "RBAC" in search field.
-3. Observe results.</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>"RBAC AND SBAC" should appear in filtered results.</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -930,7 +886,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>GROUPS_013</t>
+          <t>GROUPS_011</t>
         </is>
       </c>
       <c r="B14" s="2" t="n"/>
@@ -938,31 +894,31 @@
       <c r="D14" s="2" t="n"/>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Verify case-insensitive search</t>
+          <t>Verify search by group name</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Groups tab.
-2. Type "hello" in search field.
+2. Type "Hiking" in search field.
 3. Observe results.</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>"Hello" group should appear regardless of case used in search.</t>
+          <t>"Hiking Group" should appear in filtered results.</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>GROUPS_014</t>
+          <t>GROUPS_012</t>
         </is>
       </c>
       <c r="B15" s="2" t="n"/>
@@ -970,31 +926,31 @@
       <c r="D15" s="2" t="n"/>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Verify clearing search field</t>
+          <t>Verify search by partial name</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Groups tab.
-2. Type search query.
-3. Clear the search field.</t>
+2. Type "RBAC" in search field.
+3. Observe results.</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Full group list should be restored with all groups visible.</t>
+          <t>"RBAC AND SBAC" should appear in filtered results.</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>High / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>GROUPS_015</t>
+          <t>GROUPS_013</t>
         </is>
       </c>
       <c r="B16" s="2" t="n"/>
@@ -1002,19 +958,19 @@
       <c r="D16" s="2" t="n"/>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Verify real-time search filtering</t>
+          <t>Verify case-insensitive search</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Groups tab.
-2. Start typing in search field.
-3. Observe list updates.</t>
+2. Type "hello" in search field.
+3. Observe results.</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Group list should filter in real-time as user types each character.</t>
+          <t>"Hello" group should appear regardless of case used in search.</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1026,51 +982,39 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>GROUPS_016</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Verify Group Search</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on Groups tab</t>
-        </is>
-      </c>
+          <t>GROUPS_014</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n"/>
+      <c r="C17" s="2" t="n"/>
+      <c r="D17" s="2" t="n"/>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Verify search with no matching results</t>
+          <t>Verify clearing search field</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Groups tab.
-2. Type "XYZ123" in search field.
-3. Observe results.</t>
+2. Type search query.
+3. Clear the search field.</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Empty state should display with message like "No groups found".</t>
+          <t>Full group list should be restored with all groups visible.</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>GROUPS_017</t>
+          <t>GROUPS_015</t>
         </is>
       </c>
       <c r="B18" s="2" t="n"/>
@@ -1078,288 +1022,246 @@
       <c r="D18" s="2" t="n"/>
       <c r="E18" s="2" t="inlineStr">
         <is>
+          <t>Verify real-time search filtering</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>1. Navigate to Groups tab.
+2. Start typing in search field.
+3. Observe list updates.</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Group list should filter in real-time as user types each character.</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n"/>
+      <c r="B19" s="2" t="n"/>
+      <c r="C19" s="2" t="n"/>
+      <c r="D19" s="2" t="n"/>
+      <c r="E19" s="2" t="n"/>
+      <c r="F19" s="2" t="n"/>
+      <c r="G19" s="2" t="n"/>
+      <c r="H19" s="2" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>GROUPS_016</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Verify Group Search</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on Groups tab</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Verify search with no matching results</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>1. Navigate to Groups tab.
+2. Type "XYZ123" in search field.
+3. Observe results.</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Empty state should display with message like "No groups found".</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>GROUPS_017</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n"/>
+      <c r="C21" s="2" t="n"/>
+      <c r="D21" s="2" t="n"/>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
           <t>Verify search with special characters</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Groups tab.
 2. Type "@#$%" in search field.
 3. Observe behavior.</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>Application should handle gracefully; show no results or ignore special characters.</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>Low / Medium</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="n"/>
+      <c r="B22" s="2" t="n"/>
+      <c r="C22" s="2" t="n"/>
+      <c r="D22" s="2" t="n"/>
+      <c r="E22" s="2" t="n"/>
+      <c r="F22" s="2" t="n"/>
+      <c r="G22" s="2" t="n"/>
+      <c r="H22" s="2" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>GROUPS_018</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>Verify Group selection</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>User is logged in and on Groups tab</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>Verify clicking on group opens conversation</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Groups tab.
 2. Click on any group (e.g., "Hiking Group").
 3. Observe result.</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>Group chat/conversation window should open.</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>GROUPS_019</t>
         </is>
       </c>
-      <c r="B20" s="2" t="n"/>
-      <c r="C20" s="2" t="n"/>
-      <c r="D20" s="2" t="n"/>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="B24" s="2" t="n"/>
+      <c r="C24" s="2" t="n"/>
+      <c r="D24" s="2" t="n"/>
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Verify selected group visual feedback</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Groups tab.
 2. Click on a group.
 3. Observe visual indication.</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>Selected group should show visual highlight (background color change).</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>Medium / Low</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>GROUPS_020</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>Verify Create Group button</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>User is logged in and on Groups tab</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>Verify Create Group button is visible</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Groups tab.
 2. Observe top right corner of Groups panel.</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>Create Group button (person+ icon) should be visible.</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>GROUPS_021</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="n"/>
-      <c r="C22" s="2" t="n"/>
-      <c r="D22" s="2" t="n"/>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>Verify Create Group button click</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>1. Navigate to Groups tab.
-2. Click on Create Group button.
-3. Observe result.</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>Create Group dialog/screen should open.</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>GROUPS_022</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="n"/>
-      <c r="C23" s="2" t="n"/>
-      <c r="D23" s="2" t="n"/>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>Verify Create Group button hover state</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>1. Navigate to Groups tab.
-2. Hover over Create Group button.
-3. Observe visual feedback.</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>Button should show hover effect (color change, tooltip).</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>Low / Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>GROUPS_023</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Verify Welcome message panel</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, no group selected</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>Verify welcome message display</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>1. Navigate to Groups tab.
-2. Observe right panel without selecting any group.</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>Welcome message "Welcome to your Conversations" should display.</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>Medium / Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>GROUPS_024</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="n"/>
-      <c r="C25" s="2" t="n"/>
-      <c r="D25" s="2" t="n"/>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>Verify welcome message instruction text</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>1. Navigate to Groups tab.
-2. Read instruction text in right panel.</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>Instruction "Select a chat from the list to start exploring your messages or begin a new conversation." should display.</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>Low / Low</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>GROUPS_025</t>
+          <t>GROUPS_021</t>
         </is>
       </c>
       <c r="B26" s="2" t="n"/>
@@ -1367,149 +1269,137 @@
       <c r="D26" s="2" t="n"/>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Verify welcome message icon</t>
+          <t>Verify Create Group button click</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Groups tab.
-2. Observe icon in right panel.</t>
+2. Click on Create Group button.
+3. Observe result.</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Chat bubble icon should display above the welcome message.</t>
+          <t>Create Group dialog/screen should open.</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Low / Low</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>GROUPS_026</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>Verify UI responsiveness</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in</t>
-        </is>
-      </c>
+          <t>GROUPS_022</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n"/>
+      <c r="C27" s="2" t="n"/>
+      <c r="D27" s="2" t="n"/>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Verify Groups module on desktop browser</t>
+          <t>Verify Create Group button hover state</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1. Open application on desktop.
-2. Navigate to Groups tab.
-3. Resize browser window.</t>
+          <t>1. Navigate to Groups tab.
+2. Hover over Create Group button.
+3. Observe visual feedback.</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Layout should adjust dynamically; group list and welcome panel should remain functional.</t>
+          <t>Button should show hover effect (color change, tooltip).</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>High / Medium</t>
+          <t>Low / Low</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>GROUPS_027</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="n"/>
-      <c r="C28" s="2" t="n"/>
-      <c r="D28" s="2" t="n"/>
+          <t>GROUPS_023</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Verify Welcome message panel</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in, no group selected</t>
+        </is>
+      </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Verify Groups module on mobile device</t>
+          <t>Verify welcome message display</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1. Open application on mobile browser/device.
-2. Navigate to Groups tab.
-3. Check layout.</t>
+          <t>1. Navigate to Groups tab.
+2. Observe right panel without selecting any group.</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Group list should fit screen properly; welcome panel may be hidden on mobile.</t>
+          <t>Welcome message "Welcome to your Conversations" should display.</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>High / Medium</t>
+          <t>Medium / Low</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>GROUPS_028</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>Verify navigation</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in</t>
-        </is>
-      </c>
+          <t>GROUPS_024</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n"/>
+      <c r="C29" s="2" t="n"/>
+      <c r="D29" s="2" t="n"/>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Verify Groups tab highlight in navigation</t>
+          <t>Verify welcome message instruction text</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1. Click on Groups tab in bottom navigation.
-2. Observe tab appearance.</t>
+          <t>1. Navigate to Groups tab.
+2. Read instruction text in right panel.</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Groups tab should be highlighted/selected (purple icon).</t>
+          <t>Instruction "Select a chat from the list to start exploring your messages or begin a new conversation." should display.</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Medium / Low</t>
+          <t>Low / Low</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>GROUPS_029</t>
+          <t>GROUPS_025</t>
         </is>
       </c>
       <c r="B30" s="2" t="n"/>
@@ -1517,102 +1407,262 @@
       <c r="D30" s="2" t="n"/>
       <c r="E30" s="2" t="inlineStr">
         <is>
+          <t>Verify welcome message icon</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>1. Navigate to Groups tab.
+2. Observe icon in right panel.</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>Chat bubble icon should display above the welcome message.</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>Low / Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>GROUPS_026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Verify UI responsiveness</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Verify Groups module on desktop browser</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>1. Open application on desktop.
+2. Navigate to Groups tab.
+3. Resize browser window.</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>Layout should adjust dynamically; group list and welcome panel should remain functional.</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>High / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>GROUPS_027</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n"/>
+      <c r="C32" s="2" t="n"/>
+      <c r="D32" s="2" t="n"/>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Verify Groups module on mobile device</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>1. Open application on mobile browser/device.
+2. Navigate to Groups tab.
+3. Check layout.</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Group list should fit screen properly; welcome panel may be hidden on mobile.</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>High / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>GROUPS_028</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Verify navigation</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Verify Groups tab highlight in navigation</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>1. Click on Groups tab in bottom navigation.
+2. Observe tab appearance.</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>Groups tab should be highlighted/selected (purple icon).</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>GROUPS_029</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n"/>
+      <c r="C34" s="2" t="n"/>
+      <c r="D34" s="2" t="n"/>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
           <t>Verify navigation between tabs</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>1. Click on Groups tab.
 2. Click on Chats tab.
 3. Click back on Groups tab.</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>Navigation should work smoothly; Group list should reload correctly.</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>High / Medium</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="n"/>
+      <c r="B35" s="2" t="n"/>
+      <c r="C35" s="2" t="n"/>
+      <c r="D35" s="2" t="n"/>
+      <c r="E35" s="2" t="n"/>
+      <c r="F35" s="2" t="n"/>
+      <c r="G35" s="2" t="n"/>
+      <c r="H35" s="2" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>GROUPS_030</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>Verify Group List loading</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>User is logged in, slow network</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>Verify loading state during slow connection</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>1. Simulate slow network.
 2. Navigate to Groups tab.
 3. Observe loading behavior.</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>Loading indicator should display while group list is being fetched.</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>GROUPS_031</t>
         </is>
       </c>
-      <c r="B32" s="2" t="n"/>
-      <c r="C32" s="2" t="n"/>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="B37" s="2" t="n"/>
+      <c r="C37" s="2" t="n"/>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>User is logged in, network error</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>Verify error handling on network failure</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>1. Disconnect network.
 2. Navigate to Groups tab.
 3. Observe error handling.</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>Appropriate error message should display with retry option.</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
@@ -2118,7 +2168,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2278,35 +2328,45 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>GROUPS_043</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="n"/>
+      <c r="B5" s="2" t="n"/>
       <c r="C5" s="2" t="n"/>
       <c r="D5" s="2" t="n"/>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
+      <c r="G5" s="2" t="n"/>
+      <c r="H5" s="2" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>GROUPS_043</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n"/>
+      <c r="D6" s="2" t="n"/>
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Verify group creation without network</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>1. Disconnect network.
 2. Try to create a group.</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Error message should display. Group should not be created.</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>

--- a/Groups_Module/Groups_Module_Test_Cases.xlsx
+++ b/Groups_Module/Groups_Module_Test_Cases.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -698,195 +698,224 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n"/>
-      <c r="B8" s="2" t="n"/>
-      <c r="C8" s="2" t="n"/>
-      <c r="D8" s="2" t="n"/>
-      <c r="E8" s="2" t="n"/>
-      <c r="F8" s="2" t="n"/>
-      <c r="G8" s="2" t="n"/>
-      <c r="H8" s="2" t="n"/>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>GROUPS_009</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Verify Group List scrolling</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in, multiple groups exist</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Verify group list scrolling functionality</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1. Navigate to Groups tab.
+2. Scroll down through the list.
+3. Scroll back up.</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>List should scroll smoothly; group entries should remain properly formatted.</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>High / Medium</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>GROUPS_007</t>
+          <t>GROUPS_010</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Verify Group List display</t>
+          <t>Verify Group Search</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>User is logged in, no groups exist</t>
+          <t>User is logged in and on Groups tab</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Verify empty group list state</t>
+          <t>Verify search field is visible and accessible</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1. Navigate to Groups tab with no groups.
-2. Observe display.</t>
+          <t>1. Navigate to Groups tab.
+2. Observe search field at top.</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Empty state message should display (e.g., "No groups found" or create group prompt).</t>
+          <t>Search field should be visible with placeholder text "Search".</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>GROUPS_008</t>
+          <t>GROUPS_011</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
       <c r="C10" s="2" t="n"/>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, group has very long name</t>
-        </is>
-      </c>
+      <c r="D10" s="2" t="n"/>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Verify handling of very long group names</t>
+          <t>Verify search by group name</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Groups tab.
-2. Find group with very long name.
-3. Observe display.</t>
+2. Type "Hiking" in search field.
+3. Observe results.</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Long names should be truncated with ellipsis (...) without breaking layout.</t>
+          <t>"Hiking Group" should appear in filtered results.</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Low / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n"/>
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>GROUPS_012</t>
+        </is>
+      </c>
       <c r="B11" s="2" t="n"/>
       <c r="C11" s="2" t="n"/>
       <c r="D11" s="2" t="n"/>
-      <c r="E11" s="2" t="n"/>
-      <c r="F11" s="2" t="n"/>
-      <c r="G11" s="2" t="n"/>
-      <c r="H11" s="2" t="n"/>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Verify search by partial name</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1. Navigate to Groups tab.
+2. Type "RBAC" in search field.
+3. Observe results.</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>"RBAC AND SBAC" should appear in filtered results.</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>GROUPS_009</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Verify Group List scrolling</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, multiple groups exist</t>
-        </is>
-      </c>
+          <t>GROUPS_013</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n"/>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="2" t="n"/>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Verify group list scrolling functionality</t>
+          <t>Verify case-insensitive search</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Groups tab.
-2. Scroll down through the list.
-3. Scroll back up.</t>
+2. Type "hello" in search field.
+3. Observe results.</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>List should scroll smoothly; group entries should remain properly formatted.</t>
+          <t>"Hello" group should appear regardless of case used in search.</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>High / Medium</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>GROUPS_010</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Verify Group Search</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on Groups tab</t>
-        </is>
-      </c>
+          <t>GROUPS_014</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="2" t="n"/>
+      <c r="D13" s="2" t="n"/>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Verify search field is visible and accessible</t>
+          <t>Verify clearing search field</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Groups tab.
-2. Observe search field at top.</t>
+2. Type search query.
+3. Clear the search field.</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Search field should be visible with placeholder text "Search".</t>
+          <t>Full group list should be restored with all groups visible.</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>GROUPS_011</t>
+          <t>GROUPS_015</t>
         </is>
       </c>
       <c r="B14" s="2" t="n"/>
@@ -894,51 +923,63 @@
       <c r="D14" s="2" t="n"/>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Verify search by group name</t>
+          <t>Verify real-time search filtering</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Groups tab.
-2. Type "Hiking" in search field.
-3. Observe results.</t>
+2. Start typing in search field.
+3. Observe list updates.</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>"Hiking Group" should appear in filtered results.</t>
+          <t>Group list should filter in real-time as user types each character.</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>GROUPS_012</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n"/>
-      <c r="C15" s="2" t="n"/>
-      <c r="D15" s="2" t="n"/>
+          <t>GROUPS_018</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Verify Group selection</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on Groups tab</t>
+        </is>
+      </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Verify search by partial name</t>
+          <t>Verify clicking on group opens conversation</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Groups tab.
-2. Type "RBAC" in search field.
-3. Observe results.</t>
+2. Click on any group (e.g., "Hiking Group").
+3. Observe result.</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>"RBAC AND SBAC" should appear in filtered results.</t>
+          <t>Group chat/conversation window should open.</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -950,7 +991,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>GROUPS_013</t>
+          <t>GROUPS_019</t>
         </is>
       </c>
       <c r="B16" s="2" t="n"/>
@@ -958,63 +999,74 @@
       <c r="D16" s="2" t="n"/>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Verify case-insensitive search</t>
+          <t>Verify selected group visual feedback</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Groups tab.
-2. Type "hello" in search field.
-3. Observe results.</t>
+2. Click on a group.
+3. Observe visual indication.</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>"Hello" group should appear regardless of case used in search.</t>
+          <t>Selected group should show visual highlight (background color change).</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>Medium / Low</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>GROUPS_014</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n"/>
-      <c r="C17" s="2" t="n"/>
-      <c r="D17" s="2" t="n"/>
+          <t>GROUPS_020</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Verify Create Group button</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on Groups tab</t>
+        </is>
+      </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Verify clearing search field</t>
+          <t>Verify Create Group button is visible</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Groups tab.
-2. Type search query.
-3. Clear the search field.</t>
+2. Observe top right corner of Groups panel.</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Full group list should be restored with all groups visible.</t>
+          <t>Create Group button (person+ icon) should be visible.</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>High / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>GROUPS_015</t>
+          <t>GROUPS_021</t>
         </is>
       </c>
       <c r="B18" s="2" t="n"/>
@@ -1022,85 +1074,106 @@
       <c r="D18" s="2" t="n"/>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Verify real-time search filtering</t>
+          <t>Verify Create Group button click</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Groups tab.
-2. Start typing in search field.
-3. Observe list updates.</t>
+2. Click on Create Group button.
+3. Observe result.</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Group list should filter in real-time as user types each character.</t>
+          <t>Create Group dialog/screen should open.</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n"/>
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>GROUPS_022</t>
+        </is>
+      </c>
       <c r="B19" s="2" t="n"/>
       <c r="C19" s="2" t="n"/>
       <c r="D19" s="2" t="n"/>
-      <c r="E19" s="2" t="n"/>
-      <c r="F19" s="2" t="n"/>
-      <c r="G19" s="2" t="n"/>
-      <c r="H19" s="2" t="n"/>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Verify Create Group button hover state</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>1. Navigate to Groups tab.
+2. Hover over Create Group button.
+3. Observe visual feedback.</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Button should show hover effect (color change, tooltip).</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Low / Low</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>GROUPS_016</t>
+          <t>GROUPS_023</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Verify Group Search</t>
+          <t>Verify Welcome message panel</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>User is logged in and on Groups tab</t>
+          <t>User is logged in, no group selected</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Verify search with no matching results</t>
+          <t>Verify welcome message display</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Groups tab.
-2. Type "XYZ123" in search field.
-3. Observe results.</t>
+2. Observe right panel without selecting any group.</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Empty state should display with message like "No groups found".</t>
+          <t>Welcome message "Welcome to your Conversations" should display.</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>Medium / Low</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>GROUPS_017</t>
+          <t>GROUPS_024</t>
         </is>
       </c>
       <c r="B21" s="2" t="n"/>
@@ -1108,41 +1181,61 @@
       <c r="D21" s="2" t="n"/>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Verify search with special characters</t>
+          <t>Verify welcome message instruction text</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Groups tab.
-2. Type "@#$%" in search field.
-3. Observe behavior.</t>
+2. Read instruction text in right panel.</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Application should handle gracefully; show no results or ignore special characters.</t>
+          <t>Instruction "Select a chat from the list to start exploring your messages or begin a new conversation." should display.</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Low / Medium</t>
+          <t>Low / Low</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n"/>
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>GROUPS_025</t>
+        </is>
+      </c>
       <c r="B22" s="2" t="n"/>
       <c r="C22" s="2" t="n"/>
       <c r="D22" s="2" t="n"/>
-      <c r="E22" s="2" t="n"/>
-      <c r="F22" s="2" t="n"/>
-      <c r="G22" s="2" t="n"/>
-      <c r="H22" s="2" t="n"/>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Verify welcome message icon</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>1. Navigate to Groups tab.
+2. Observe icon in right panel.</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Chat bubble icon should display above the welcome message.</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Low / Low</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>GROUPS_018</t>
+          <t>GROUPS_026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1152,41 +1245,41 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Verify Group selection</t>
+          <t>Verify UI responsiveness</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>User is logged in and on Groups tab</t>
+          <t>User is logged in</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Verify clicking on group opens conversation</t>
+          <t>Verify Groups module on desktop browser</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1. Navigate to Groups tab.
-2. Click on any group (e.g., "Hiking Group").
-3. Observe result.</t>
+          <t>1. Open application on desktop.
+2. Navigate to Groups tab.
+3. Resize browser window.</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Group chat/conversation window should open.</t>
+          <t>Layout should adjust dynamically; group list and welcome panel should remain functional.</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>GROUPS_019</t>
+          <t>GROUPS_027</t>
         </is>
       </c>
       <c r="B24" s="2" t="n"/>
@@ -1194,31 +1287,31 @@
       <c r="D24" s="2" t="n"/>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Verify selected group visual feedback</t>
+          <t>Verify Groups module on mobile device</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1. Navigate to Groups tab.
-2. Click on a group.
-3. Observe visual indication.</t>
+          <t>1. Open application on mobile browser/device.
+2. Navigate to Groups tab.
+3. Check layout.</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Selected group should show visual highlight (background color change).</t>
+          <t>Group list should fit screen properly; welcome panel may be hidden on mobile.</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Medium / Low</t>
+          <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>GROUPS_020</t>
+          <t>GROUPS_028</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1228,40 +1321,40 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Verify Create Group button</t>
+          <t>Verify navigation</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>User is logged in and on Groups tab</t>
+          <t>User is logged in</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Verify Create Group button is visible</t>
+          <t>Verify Groups tab highlight in navigation</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1. Navigate to Groups tab.
-2. Observe top right corner of Groups panel.</t>
+          <t>1. Click on Groups tab in bottom navigation.
+2. Observe tab appearance.</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Create Group button (person+ icon) should be visible.</t>
+          <t>Groups tab should be highlighted/selected (purple icon).</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>Medium / Low</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>GROUPS_021</t>
+          <t>GROUPS_029</t>
         </is>
       </c>
       <c r="B26" s="2" t="n"/>
@@ -1269,400 +1362,267 @@
       <c r="D26" s="2" t="n"/>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Verify Create Group button click</t>
+          <t>Verify navigation between tabs</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1. Navigate to Groups tab.
-2. Click on Create Group button.
-3. Observe result.</t>
+          <t>1. Click on Groups tab.
+2. Click on Chats tab.
+3. Click back on Groups tab.</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Create Group dialog/screen should open.</t>
+          <t>Navigation should work smoothly; Group list should reload correctly.</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>GROUPS_022</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="n"/>
       <c r="B27" s="2" t="n"/>
       <c r="C27" s="2" t="n"/>
       <c r="D27" s="2" t="n"/>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>Verify Create Group button hover state</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>1. Navigate to Groups tab.
-2. Hover over Create Group button.
-3. Observe visual feedback.</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>Button should show hover effect (color change, tooltip).</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>Low / Low</t>
-        </is>
-      </c>
+      <c r="E27" s="2" t="n"/>
+      <c r="F27" s="2" t="n"/>
+      <c r="G27" s="2" t="n"/>
+      <c r="H27" s="2" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>GROUPS_023</t>
+          <t>GROUPS_007</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Verify Welcome message panel</t>
+          <t>Verify Group List display</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>User is logged in, no group selected</t>
+          <t>User is logged in, no groups exist</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Verify welcome message display</t>
+          <t>Verify empty group list state</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1. Navigate to Groups tab.
-2. Observe right panel without selecting any group.</t>
+          <t>1. Navigate to Groups tab with no groups.
+2. Observe display.</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Welcome message "Welcome to your Conversations" should display.</t>
+          <t>Empty state message should display (e.g., "No groups found" or create group prompt).</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Medium / Low</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>GROUPS_024</t>
+          <t>GROUPS_008</t>
         </is>
       </c>
       <c r="B29" s="2" t="n"/>
       <c r="C29" s="2" t="n"/>
-      <c r="D29" s="2" t="n"/>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in, group has very long name</t>
+        </is>
+      </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Verify welcome message instruction text</t>
+          <t>Verify handling of very long group names</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Groups tab.
-2. Read instruction text in right panel.</t>
+2. Find group with very long name.
+3. Observe display.</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Instruction "Select a chat from the list to start exploring your messages or begin a new conversation." should display.</t>
+          <t>Long names should be truncated with ellipsis (...) without breaking layout.</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Low / Low</t>
+          <t>Low / Medium</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>GROUPS_025</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="n"/>
-      <c r="C30" s="2" t="n"/>
-      <c r="D30" s="2" t="n"/>
+          <t>GROUPS_016</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Verify Group Search</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on Groups tab</t>
+        </is>
+      </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Verify welcome message icon</t>
+          <t>Verify search with no matching results</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Groups tab.
-2. Observe icon in right panel.</t>
+2. Type "XYZ123" in search field.
+3. Observe results.</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Chat bubble icon should display above the welcome message.</t>
+          <t>Empty state should display with message like "No groups found".</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Low / Low</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>GROUPS_026</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>Verify UI responsiveness</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in</t>
-        </is>
-      </c>
+          <t>GROUPS_017</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n"/>
+      <c r="C31" s="2" t="n"/>
+      <c r="D31" s="2" t="n"/>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Verify Groups module on desktop browser</t>
+          <t>Verify search with special characters</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1. Open application on desktop.
-2. Navigate to Groups tab.
-3. Resize browser window.</t>
+          <t>1. Navigate to Groups tab.
+2. Type "@#$%" in search field.
+3. Observe behavior.</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Layout should adjust dynamically; group list and welcome panel should remain functional.</t>
+          <t>Application should handle gracefully; show no results or ignore special characters.</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>High / Medium</t>
+          <t>Low / Medium</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>GROUPS_027</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="n"/>
-      <c r="C32" s="2" t="n"/>
-      <c r="D32" s="2" t="n"/>
+          <t>GROUPS_030</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Verify Group List loading</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in, slow network</t>
+        </is>
+      </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Verify Groups module on mobile device</t>
+          <t>Verify loading state during slow connection</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>1. Open application on mobile browser/device.
-2. Navigate to Groups tab.
-3. Check layout.</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>Group list should fit screen properly; welcome panel may be hidden on mobile.</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>High / Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>GROUPS_028</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>Verify navigation</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>Verify Groups tab highlight in navigation</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>1. Click on Groups tab in bottom navigation.
-2. Observe tab appearance.</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>Groups tab should be highlighted/selected (purple icon).</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>Medium / Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>GROUPS_029</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="n"/>
-      <c r="C34" s="2" t="n"/>
-      <c r="D34" s="2" t="n"/>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>Verify navigation between tabs</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>1. Click on Groups tab.
-2. Click on Chats tab.
-3. Click back on Groups tab.</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>Navigation should work smoothly; Group list should reload correctly.</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>High / Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="n"/>
-      <c r="B35" s="2" t="n"/>
-      <c r="C35" s="2" t="n"/>
-      <c r="D35" s="2" t="n"/>
-      <c r="E35" s="2" t="n"/>
-      <c r="F35" s="2" t="n"/>
-      <c r="G35" s="2" t="n"/>
-      <c r="H35" s="2" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>GROUPS_030</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>Verify Group List loading</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, slow network</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>Verify loading state during slow connection</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>1. Simulate slow network.
 2. Navigate to Groups tab.
 3. Observe loading behavior.</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>Loading indicator should display while group list is being fetched.</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>GROUPS_031</t>
         </is>
       </c>
-      <c r="B37" s="2" t="n"/>
-      <c r="C37" s="2" t="n"/>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="B33" s="2" t="n"/>
+      <c r="C33" s="2" t="n"/>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>User is logged in, network error</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>Verify error handling on network failure</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>1. Disconnect network.
 2. Navigate to Groups tab.
 3. Observe error handling.</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>Appropriate error message should display with retry option.</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>

--- a/Groups_Module/Groups_Module_Test_Cases.xlsx
+++ b/Groups_Module/Groups_Module_Test_Cases.xlsx
@@ -23,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,8 +36,18 @@
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -48,6 +58,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="004472C4"/>
         <bgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+        <bgColor rgb="001F4E79"/>
       </patternFill>
     </fill>
   </fills>
@@ -69,13 +85,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -443,1188 +465,1605 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>TestCase_ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Sentiment</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Test Scenario</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Precondition</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Test Case</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Expected Results</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Priority / Severity</t>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Priority/Severity</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>GROUPS_001</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>Verify Group List display</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>User is logged in and navigated to Groups tab</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>Verify group list loads correctly</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. Login to application.
 2. Click on "Groups" tab in bottom navigation.
 3. Observe group list.</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>Group list should display with group names, member counts, and group avatars.</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>GROUPS_002</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>Verify group name display</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>1. Navigate to Groups tab.
 2. Observe group names in the list.</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>Group names should display clearly (e.g., "Hiking Group", "RBAC AND SBAC", "Hello").</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>GROUPS_003</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n"/>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>Verify group avatar/icon display</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1. Navigate to Groups tab.
 2. Observe avatars next to each group.</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>Group avatars should display correctly; default initials avatar for groups without custom image.</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>Medium / Low</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>GROUPS_004</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n"/>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="n"/>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>Verify member count display</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>1. Navigate to Groups tab.
 2. Observe member count below each group name.</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>Member count should display (e.g., "5 Members", "4 Members", "1 Member").</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>GROUPS_005</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n"/>
-      <c r="C6" s="2" t="n"/>
-      <c r="D6" s="2" t="n"/>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>Verify online status indicator</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>1. Navigate to Groups tab.
 2. Observe online indicator on group avatars.</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>Green dot should indicate active members in the group.</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>Low / Low</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>GROUPS_006</t>
         </is>
       </c>
-      <c r="B7" s="2" t="n"/>
-      <c r="C7" s="2" t="n"/>
-      <c r="D7" s="2" t="n"/>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="B7" s="4" t="n"/>
+      <c r="C7" s="4" t="n"/>
+      <c r="D7" s="4" t="n"/>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>Verify group initials avatar display</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>1. Navigate to Groups tab.
 2. Find group with initials avatar (e.g., "RA", "HE").</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>Initials should display in colored circle for groups without custom image.</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>GROUPS_009</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>Verify Group List scrolling</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>User is logged in, multiple groups exist</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>Verify group list scrolling functionality</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>1. Navigate to Groups tab.
 2. Scroll down through the list.
 3. Scroll back up.</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>List should scroll smoothly; group entries should remain properly formatted.</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>GROUPS_010</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>Verify Group Search</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>User is logged in and on Groups tab</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>Verify search field is visible and accessible</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>1. Navigate to Groups tab.
 2. Observe search field at top.</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>Search field should be visible with placeholder text "Search".</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>GROUPS_011</t>
         </is>
       </c>
-      <c r="B10" s="2" t="n"/>
-      <c r="C10" s="2" t="n"/>
-      <c r="D10" s="2" t="n"/>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="B10" s="4" t="n"/>
+      <c r="C10" s="4" t="n"/>
+      <c r="D10" s="4" t="n"/>
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>Verify search by group name</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>1. Navigate to Groups tab.
 2. Type "Hiking" in search field.
 3. Observe results.</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>"Hiking Group" should appear in filtered results.</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H10" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>GROUPS_012</t>
         </is>
       </c>
-      <c r="B11" s="2" t="n"/>
-      <c r="C11" s="2" t="n"/>
-      <c r="D11" s="2" t="n"/>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="B11" s="4" t="n"/>
+      <c r="C11" s="4" t="n"/>
+      <c r="D11" s="4" t="n"/>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>Verify search by partial name</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>1. Navigate to Groups tab.
 2. Type "RBAC" in search field.
 3. Observe results.</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>"RBAC AND SBAC" should appear in filtered results.</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>GROUPS_013</t>
         </is>
       </c>
-      <c r="B12" s="2" t="n"/>
-      <c r="C12" s="2" t="n"/>
-      <c r="D12" s="2" t="n"/>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="B12" s="4" t="n"/>
+      <c r="C12" s="4" t="n"/>
+      <c r="D12" s="4" t="n"/>
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>Verify case-insensitive search</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>1. Navigate to Groups tab.
 2. Type "hello" in search field.
 3. Observe results.</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>"Hello" group should appear regardless of case used in search.</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H12" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>GROUPS_014</t>
         </is>
       </c>
-      <c r="B13" s="2" t="n"/>
-      <c r="C13" s="2" t="n"/>
-      <c r="D13" s="2" t="n"/>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="B13" s="4" t="n"/>
+      <c r="C13" s="4" t="n"/>
+      <c r="D13" s="4" t="n"/>
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>Verify clearing search field</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>1. Navigate to Groups tab.
 2. Type search query.
 3. Clear the search field.</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>Full group list should be restored with all groups visible.</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H13" s="4" t="inlineStr">
         <is>
           <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>GROUPS_015</t>
         </is>
       </c>
-      <c r="B14" s="2" t="n"/>
-      <c r="C14" s="2" t="n"/>
-      <c r="D14" s="2" t="n"/>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="B14" s="4" t="n"/>
+      <c r="C14" s="4" t="n"/>
+      <c r="D14" s="4" t="n"/>
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>Verify real-time search filtering</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>1. Navigate to Groups tab.
 2. Start typing in search field.
 3. Observe list updates.</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>Group list should filter in real-time as user types each character.</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H14" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>GROUPS_018</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>Verify Group selection</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>User is logged in and on Groups tab</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>Verify clicking on group opens conversation</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>1. Navigate to Groups tab.
 2. Click on any group (e.g., "Hiking Group").
 3. Observe result.</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>Group chat/conversation window should open.</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H15" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>GROUPS_019</t>
         </is>
       </c>
-      <c r="B16" s="2" t="n"/>
-      <c r="C16" s="2" t="n"/>
-      <c r="D16" s="2" t="n"/>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="B16" s="4" t="n"/>
+      <c r="C16" s="4" t="n"/>
+      <c r="D16" s="4" t="n"/>
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>Verify selected group visual feedback</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>1. Navigate to Groups tab.
 2. Click on a group.
 3. Observe visual indication.</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>Selected group should show visual highlight (background color change).</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H16" s="4" t="inlineStr">
         <is>
           <t>Medium / Low</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>GROUPS_020</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>Verify Create Group button</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>User is logged in and on Groups tab</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>Verify Create Group button is visible</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>1. Navigate to Groups tab.
 2. Observe top right corner of Groups panel.</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>Create Group button (person+ icon) should be visible.</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H17" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>GROUPS_021</t>
         </is>
       </c>
-      <c r="B18" s="2" t="n"/>
-      <c r="C18" s="2" t="n"/>
-      <c r="D18" s="2" t="n"/>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="B18" s="4" t="n"/>
+      <c r="C18" s="4" t="n"/>
+      <c r="D18" s="4" t="n"/>
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t>Verify Create Group button click</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F18" s="4" t="inlineStr">
         <is>
           <t>1. Navigate to Groups tab.
 2. Click on Create Group button.
 3. Observe result.</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
         <is>
           <t>Create Group dialog/screen should open.</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H18" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>GROUPS_022</t>
         </is>
       </c>
-      <c r="B19" s="2" t="n"/>
-      <c r="C19" s="2" t="n"/>
-      <c r="D19" s="2" t="n"/>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="B19" s="4" t="n"/>
+      <c r="C19" s="4" t="n"/>
+      <c r="D19" s="4" t="n"/>
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>Verify Create Group button hover state</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>1. Navigate to Groups tab.
 2. Hover over Create Group button.
 3. Observe visual feedback.</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>Button should show hover effect (color change, tooltip).</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="H19" s="4" t="inlineStr">
         <is>
           <t>Low / Low</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>GROUPS_023</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>Verify Welcome message panel</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>User is logged in, no group selected</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>Verify welcome message display</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>1. Navigate to Groups tab.
 2. Observe right panel without selecting any group.</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>Welcome message "Welcome to your Conversations" should display.</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H20" s="4" t="inlineStr">
         <is>
           <t>Medium / Low</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>GROUPS_024</t>
         </is>
       </c>
-      <c r="B21" s="2" t="n"/>
-      <c r="C21" s="2" t="n"/>
-      <c r="D21" s="2" t="n"/>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="B21" s="4" t="n"/>
+      <c r="C21" s="4" t="n"/>
+      <c r="D21" s="4" t="n"/>
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>Verify welcome message instruction text</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F21" s="4" t="inlineStr">
         <is>
           <t>1. Navigate to Groups tab.
 2. Read instruction text in right panel.</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>Instruction "Select a chat from the list to start exploring your messages or begin a new conversation." should display.</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="H21" s="4" t="inlineStr">
         <is>
           <t>Low / Low</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>GROUPS_025</t>
         </is>
       </c>
-      <c r="B22" s="2" t="n"/>
-      <c r="C22" s="2" t="n"/>
-      <c r="D22" s="2" t="n"/>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="B22" s="4" t="n"/>
+      <c r="C22" s="4" t="n"/>
+      <c r="D22" s="4" t="n"/>
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t>Verify welcome message icon</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>1. Navigate to Groups tab.
 2. Observe icon in right panel.</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>Chat bubble icon should display above the welcome message.</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H22" s="4" t="inlineStr">
         <is>
           <t>Low / Low</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>GROUPS_026</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>Verify UI responsiveness</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E23" s="4" t="inlineStr">
         <is>
           <t>Verify Groups module on desktop browser</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F23" s="4" t="inlineStr">
         <is>
           <t>1. Open application on desktop.
 2. Navigate to Groups tab.
 3. Resize browser window.</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G23" s="4" t="inlineStr">
         <is>
           <t>Layout should adjust dynamically; group list and welcome panel should remain functional.</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="H23" s="4" t="inlineStr">
         <is>
           <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>GROUPS_027</t>
         </is>
       </c>
-      <c r="B24" s="2" t="n"/>
-      <c r="C24" s="2" t="n"/>
-      <c r="D24" s="2" t="n"/>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="B24" s="4" t="n"/>
+      <c r="C24" s="4" t="n"/>
+      <c r="D24" s="4" t="n"/>
+      <c r="E24" s="4" t="inlineStr">
         <is>
           <t>Verify Groups module on mobile device</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F24" s="4" t="inlineStr">
         <is>
           <t>1. Open application on mobile browser/device.
 2. Navigate to Groups tab.
 3. Check layout.</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G24" s="4" t="inlineStr">
         <is>
           <t>Group list should fit screen properly; welcome panel may be hidden on mobile.</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="H24" s="4" t="inlineStr">
         <is>
           <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>GROUPS_028</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>Verify navigation</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E25" s="4" t="inlineStr">
         <is>
           <t>Verify Groups tab highlight in navigation</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F25" s="4" t="inlineStr">
         <is>
           <t>1. Click on Groups tab in bottom navigation.
 2. Observe tab appearance.</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G25" s="4" t="inlineStr">
         <is>
           <t>Groups tab should be highlighted/selected (purple icon).</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="H25" s="4" t="inlineStr">
         <is>
           <t>Medium / Low</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>GROUPS_029</t>
         </is>
       </c>
-      <c r="B26" s="2" t="n"/>
-      <c r="C26" s="2" t="n"/>
-      <c r="D26" s="2" t="n"/>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="B26" s="4" t="n"/>
+      <c r="C26" s="4" t="n"/>
+      <c r="D26" s="4" t="n"/>
+      <c r="E26" s="4" t="inlineStr">
         <is>
           <t>Verify navigation between tabs</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F26" s="4" t="inlineStr">
         <is>
           <t>1. Click on Groups tab.
 2. Click on Chats tab.
 3. Click back on Groups tab.</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G26" s="4" t="inlineStr">
         <is>
           <t>Navigation should work smoothly; Group list should reload correctly.</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="H26" s="4" t="inlineStr">
         <is>
           <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n"/>
-      <c r="B27" s="2" t="n"/>
-      <c r="C27" s="2" t="n"/>
-      <c r="D27" s="2" t="n"/>
-      <c r="E27" s="2" t="n"/>
-      <c r="F27" s="2" t="n"/>
-      <c r="G27" s="2" t="n"/>
-      <c r="H27" s="2" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>GROUPS_007</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>Verify Group List display</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, no groups exist</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>Verify empty group list state</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>1. Navigate to Groups tab with no groups.
-2. Observe display.</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>Empty state message should display (e.g., "No groups found" or create group prompt).</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>GROUPS_008</t>
         </is>
       </c>
-      <c r="B29" s="2" t="n"/>
-      <c r="C29" s="2" t="n"/>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="B27" s="4" t="n"/>
+      <c r="C27" s="4" t="n"/>
+      <c r="D27" s="4" t="inlineStr">
         <is>
           <t>User is logged in, group has very long name</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E27" s="4" t="inlineStr">
         <is>
           <t>Verify handling of very long group names</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F27" s="4" t="inlineStr">
         <is>
           <t>1. Navigate to Groups tab.
 2. Find group with very long name.
 3. Observe display.</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G27" s="4" t="inlineStr">
         <is>
           <t>Long names should be truncated with ellipsis (...) without breaking layout.</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="H27" s="4" t="inlineStr">
         <is>
           <t>Low / Medium</t>
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>GROUPS_017</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="n"/>
+      <c r="C28" s="4" t="n"/>
+      <c r="D28" s="4" t="n"/>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>Verify search with special characters</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>1. Navigate to Groups tab.
+2. Type "@#$%" in search field.
+3. Observe behavior.</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>Application should handle gracefully; show no results or ignore special characters.</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>Low / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>GROUPS_031</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="n"/>
+      <c r="C29" s="4" t="n"/>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>User is logged in, network error</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>Verify error handling on network failure</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>1. Disconnect network.
+2. Navigate to Groups tab.
+3. Observe error handling.</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>Appropriate error message should display with retry option.</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>GM_001</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Join Password Group</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>Password protected group exists</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>Verify password dialog appears for password group</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>1. Click on password protected group
+2. Check for dialog</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>Password input dialog appears</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>GM_002</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>Join Password Group - Correct</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>Password dialog open</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>Verify joining with correct password</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>1. Enter correct password
+2. Click join</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>User joins group successfully</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>GM_003</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>Join Password Group - UI</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>Password dialog open</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>Verify password dialog has input and join button</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>1. Check dialog elements</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>Password input field and Join button visible</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>GM_004</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>Group Type Icons in List</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>Groups list with mixed types</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>Verify group type icons in groups list</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>1. Open groups list
+2. Check each group item</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>Public/private/password icons shown correctly</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>GM_005</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>Public Group Icon</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>Public group in list</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>Verify public group has correct icon</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>1. Check public group item</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>Public/open icon displayed</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>GM_006</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>Private Group Icon</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>Private group in list</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>Verify private group has lock icon</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>1. Check private group item</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>Lock/private icon displayed</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>GM_007</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>Password Group Icon</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>Password group in list</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>Verify password group has shield icon</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>1. Check password group item</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>Shield/password icon displayed</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="37"/>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>GROUPS_007</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>Verify Group List display</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>User is logged in, no groups exist</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>Verify empty group list state</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>1. Navigate to Groups tab with no groups.
+2. Observe display.</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>Empty state message should display (e.g., "No groups found" or create group prompt).</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t>GROUPS_016</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>Verify Group Search</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D39" s="4" t="inlineStr">
         <is>
           <t>User is logged in and on Groups tab</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E39" s="4" t="inlineStr">
         <is>
           <t>Verify search with no matching results</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F39" s="4" t="inlineStr">
         <is>
           <t>1. Navigate to Groups tab.
 2. Type "XYZ123" in search field.
 3. Observe results.</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G39" s="4" t="inlineStr">
         <is>
           <t>Empty state should display with message like "No groups found".</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H39" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>GROUPS_017</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="n"/>
-      <c r="C31" s="2" t="n"/>
-      <c r="D31" s="2" t="n"/>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>Verify search with special characters</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>1. Navigate to Groups tab.
-2. Type "@#$%" in search field.
-3. Observe behavior.</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>Application should handle gracefully; show no results or ignore special characters.</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>Low / Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
         <is>
           <t>GROUPS_030</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B40" s="4" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C40" s="4" t="inlineStr">
         <is>
           <t>Verify Group List loading</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D40" s="4" t="inlineStr">
         <is>
           <t>User is logged in, slow network</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E40" s="4" t="inlineStr">
         <is>
           <t>Verify loading state during slow connection</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F40" s="4" t="inlineStr">
         <is>
           <t>1. Simulate slow network.
 2. Navigate to Groups tab.
 3. Observe loading behavior.</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G40" s="4" t="inlineStr">
         <is>
           <t>Loading indicator should display while group list is being fetched.</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="H40" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>GROUPS_031</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="n"/>
-      <c r="C33" s="2" t="n"/>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, network error</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>Verify error handling on network failure</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>1. Disconnect network.
-2. Navigate to Groups tab.
-3. Observe error handling.</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>Appropriate error message should display with retry option.</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>GM_008</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>Join Password - Wrong Password</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>Password dialog open</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>Verify wrong password rejected</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>1. Enter incorrect password
+2. Click join</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>Error message shown, user not joined</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>GM_009</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>Join Password - Empty Password</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>Password dialog open</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>Verify empty password rejected</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>1. Leave password empty
+2. Click join</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t>Validation error, join button disabled or error shown</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>GM_010</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>Group Type Hidden</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>hideGroupType=true in conversations</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>Verify group type icons hidden when configured</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>1. Set hideGroupType=true
+2. Check groups</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="inlineStr">
+        <is>
+          <t>No group type icons visible</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1636,139 +2075,270 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="0070AD47"/>
+    <tabColor rgb="00548235"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>TestCase_ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Sentiment</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Test Scenario</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Precondition</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Test Case</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Expected Results</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Priority / Severity</t>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Priority/Severity</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>GROUPS_032</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>Integration: Groups Module with Chat</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>User is logged in and on Groups tab</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>Verify clicking group opens group chat</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. Click on a group in the list.
 2. Observe chat area.</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>Group chat should open with message history and group header info.</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>GROUPS_033</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>Integration: Groups Module with Group Actions</t>
         </is>
       </c>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>Verify group info accessible from group list</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>1. Long press or click info on a group in the list.</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>Group info/actions panel should open.</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>GM_011</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Password Join + Conversation</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Joined password group</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Verify conversation created after joining</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>1. Join password group
+2. Check conversation list</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>New conversation appears for joined group</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>GM_012</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Group Type + Details</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Group with type icon</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Verify type icon consistent in details view</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>1. Click group
+2. Check details</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Same type icon shown in details</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>GM_013</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Password Join + Network Loss</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Network drops during join</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Verify join fails gracefully on network loss</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1. Enter password
+2. Disconnect
+3. Click join</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Error shown, user not joined</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1780,167 +2350,254 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00FFC000"/>
+    <tabColor rgb="00BF8F00"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>TestCase_ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Sentiment</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Test Scenario</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Precondition</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Test Case</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Expected Results</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Priority / Severity</t>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Priority/Severity</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>GROUPS_034</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>Regression: Groups Module</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>Verify group list updates after creating a new group</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. Create a new group.
 2. Go back to group list.</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>Newly created group should appear in the list.</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>GROUPS_035</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>Verify group list updates after leaving a group</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>1. Leave a group.
 2. Observe group list.</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>Left group should be removed from the list or marked appropriately.</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>GROUPS_036</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n"/>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>Verify group list after deleting a group</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1. Delete a group (as owner).
 2. Observe group list.</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>Deleted group should be removed from the list for all members.</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>GM_014</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Password After Group Type Change</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Group type changed to password</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Verify password dialog appears for changed group</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>1. Admin changes group to password type
+2. New user tries to join</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Password dialog shown for newly password-protected group</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>GM_015</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Icon After Type Change</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Group type changed</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Verify icon updates after type change</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1. Change group type
+2. Check list</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Icon updated to reflect new type</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1952,167 +2609,296 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00FF0000"/>
+    <tabColor rgb="00C00000"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>TestCase_ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Sentiment</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Test Scenario</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Precondition</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Test Case</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Expected Results</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Priority / Severity</t>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Priority/Severity</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>GROUPS_037</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Security: Groups Module</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Verify private groups not visible to non-members</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>1. Observe group list as a non-member.</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Private groups should not appear in the group list for non-members.</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>High / Critical</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>GROUPS_038</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="B2" s="4" t="n"/>
+      <c r="C2" s="4" t="n"/>
+      <c r="D2" s="4" t="n"/>
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>Verify password-protected group requires password to join</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. Click join on a password-protected group.
 2. Enter wrong password.</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>Should reject with 'Incorrect password' error. Should not allow entry.</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>High / Critical</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>GROUPS_039</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n"/>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>Verify group creation validates input</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>1. Try to create a group with empty name.
 2. Try with special characters.
 3. Try with very long name.</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>Empty name should be rejected. Special chars should be handled. Long name should truncate or reject.</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>GM_016</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Password Not Visible</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Typing password</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Verify password field masks input</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>1. Type in password field
+2. Check display</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Password characters masked (dots/asterisks)</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>GROUPS_037</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Security: Groups Module</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Verify private groups not visible to non-members</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>1. Observe group list as a non-member.</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Private groups should not appear in the group list for non-members.</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>High / Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>GM_017</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Brute Force Password</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Multiple wrong attempts</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Verify rate limiting on password attempts</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1. Enter wrong password 10+ times rapidly</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Rate limiting or lockout after multiple failures</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>GM_018</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Password in Network</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Join request sent</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Verify password encrypted in transit</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>1. Monitor network during join
+2. Check password</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>Password not visible in plain text in network</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -2128,207 +2914,327 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>TestCase_ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Sentiment</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Test Scenario</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Precondition</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Test Case</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Expected Results</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Priority / Severity</t>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Priority/Severity</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>GROUPS_040</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>Edge Case: Groups Module</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>Verify group list with 500+ groups</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. Have an account that's part of 500+ groups.
 2. Open groups tab.</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>Groups should load with pagination/infinite scroll. No performance issues.</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>Medium / High</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>GROUPS_041</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>Verify creating group with duplicate name</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>1. Create a group with a name that already exists.</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>Should either allow (with different ID) or show warning about duplicate name.</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>GROUPS_042</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n"/>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>Verify group with emoji in name</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1. Create a group named '🚀 Rocket Team'.
 2. Observe in group list.</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>Group name with emoji should display correctly.</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>Low / Low</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n"/>
-      <c r="B5" s="2" t="n"/>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="n"/>
-      <c r="E5" s="2" t="n"/>
-      <c r="F5" s="2" t="n"/>
-      <c r="G5" s="2" t="n"/>
-      <c r="H5" s="2" t="n"/>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>GM_019</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Password with Special Chars</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Password has special characters</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Verify special character password works</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>1. Set password with !@#$%
+2. Join with same password</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Join successful with special char password</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>GM_020</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Very Long Password</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Password with 100+ characters</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Verify long password handling</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>1. Enter 100+ char password
+2. Join</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Long password accepted or appropriate limit shown</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>GROUPS_043</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C6" s="2" t="n"/>
-      <c r="D6" s="2" t="n"/>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="C8" s="4" t="n"/>
+      <c r="D8" s="4" t="n"/>
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>Verify group creation without network</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>1. Disconnect network.
 2. Try to create a group.</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>Error message should display. Group should not be created.</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>GM_021</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Unicode Password</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Password with unicode/emoji</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Verify unicode password handling</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>1. Enter emoji password
+2. Join</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>Appropriate handling of unicode password</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -2344,160 +3250,246 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>TestCase_ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Sentiment</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Test Scenario</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Precondition</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Test Case</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Expected Results</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Priority / Severity</t>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Priority/Severity</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>GROUPS_044</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>Boundary: Groups Module</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>Verify group list with exactly 0 groups</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. Login with account not part of any group.</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>Empty state should display with 'No groups' message and create button.</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>GROUPS_045</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>Verify group name with exactly 1 character</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>1. Create a group with name 'A'.</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>Group should be created successfully with single character name.</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>Low / Low</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>GROUPS_046</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n"/>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>Verify group name at maximum length</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1. Create a group with name at max character limit.</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>Group should be created. Name should display (possibly truncated in list).</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>GM_022</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Password Min Length 1</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>1 character password</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Verify minimum password length</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>1. Set 1 char password
+2. Join with it</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>1 char password accepted</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>GM_023</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Password Max Length</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Very long password</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Verify password max length handling</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1. Enter extremely long password</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Appropriate max length enforced</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -2513,164 +3505,291 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>TestCase_ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Sentiment</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Test Scenario</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Precondition</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Test Case</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Expected Results</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Priority / Severity</t>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Priority/Severity</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>GROUPS_047</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>Equivalence Partitioning: Group Types</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>Verify public group display and join</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. Observe a public group in list.
 2. Click join.</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>Public group should show join button. Joining should be immediate without approval.</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>GROUPS_048</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>Verify private group display and join</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>1. Observe a private group (if visible).
 2. Try to join.</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>Private group should require invitation. No direct join option.</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>GROUPS_049</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n"/>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>Verify password-protected group display and join</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1. Observe a password-protected group.
 2. Click join.
 3. Enter correct password.</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>Should prompt for password. Correct password should allow joining.</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>GM_024</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Join Public Group</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Public group</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Verify direct join for public group</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>1. Click join on public group</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>User joins immediately without password</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>GM_025</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Join Password Group</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Password group</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Verify password required for password group</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>1. Click join on password group</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Password dialog shown before join</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>GM_026</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Join Private Group</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Private group</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Verify cannot join private group directly</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>1. Try to join private group</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>Cannot join, must be invited</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
     </row>

--- a/Groups_Module/Groups_Module_Test_Cases.xlsx
+++ b/Groups_Module/Groups_Module_Test_Cases.xlsx
@@ -67,7 +67,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -81,11 +81,12 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -97,6 +98,13 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -465,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:H65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -521,1547 +529,2500 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>GROUPS_001</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>Verify Group List display</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>User is logged in and navigated to Groups tab</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>Verify group list loads correctly</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" s="5" t="inlineStr">
         <is>
           <t>1. Login to application.
 2. Click on "Groups" tab in bottom navigation.
 3. Observe group list.</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>Group list should display with group names, member counts, and group avatars.</t>
         </is>
       </c>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>GROUPS_002</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n"/>
-      <c r="C3" s="4" t="n"/>
-      <c r="D3" s="4" t="n"/>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>Verify group name display</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>1. Navigate to Groups tab.
 2. Observe group names in the list.</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>Group names should display clearly (e.g., "Hiking Group", "RBAC AND SBAC", "Hello").</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>GROUPS_003</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>Verify group avatar/icon display</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>1. Navigate to Groups tab.
 2. Observe avatars next to each group.</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>Group avatars should display correctly; default initials avatar for groups without custom image.</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>Medium / Low</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>GROUPS_004</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n"/>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>Verify member count display</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>1. Navigate to Groups tab.
 2. Observe member count below each group name.</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>Member count should display (e.g., "5 Members", "4 Members", "1 Member").</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>GROUPS_005</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n"/>
-      <c r="C6" s="4" t="n"/>
-      <c r="D6" s="4" t="n"/>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>Verify online status indicator</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>1. Navigate to Groups tab.
 2. Observe online indicator on group avatars.</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>Green dot should indicate active members in the group.</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>Low / Low</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>GROUPS_006</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n"/>
-      <c r="C7" s="4" t="n"/>
-      <c r="D7" s="4" t="n"/>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>Verify group initials avatar display</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>1. Navigate to Groups tab.
 2. Find group with initials avatar (e.g., "RA", "HE").</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>Initials should display in colored circle for groups without custom image.</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>GROUPS_009</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>Verify Group List scrolling</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>User is logged in, multiple groups exist</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>Verify group list scrolling functionality</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>1. Navigate to Groups tab.
 2. Scroll down through the list.
 3. Scroll back up.</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>List should scroll smoothly; group entries should remain properly formatted.</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>GROUPS_010</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>Verify Group Search</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>User is logged in and on Groups tab</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>Verify search field is visible and accessible</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>1. Navigate to Groups tab.
 2. Observe search field at top.</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>Search field should be visible with placeholder text "Search".</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>GROUPS_011</t>
         </is>
       </c>
-      <c r="B10" s="4" t="n"/>
-      <c r="C10" s="4" t="n"/>
-      <c r="D10" s="4" t="n"/>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>Verify search by group name</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>1. Navigate to Groups tab.
 2. Type "Hiking" in search field.
 3. Observe results.</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>"Hiking Group" should appear in filtered results.</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>GROUPS_012</t>
         </is>
       </c>
-      <c r="B11" s="4" t="n"/>
-      <c r="C11" s="4" t="n"/>
-      <c r="D11" s="4" t="n"/>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>Verify search by partial name</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>1. Navigate to Groups tab.
 2. Type "RBAC" in search field.
 3. Observe results.</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>"RBAC AND SBAC" should appear in filtered results.</t>
         </is>
       </c>
-      <c r="H11" s="4" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>GROUPS_013</t>
         </is>
       </c>
-      <c r="B12" s="4" t="n"/>
-      <c r="C12" s="4" t="n"/>
-      <c r="D12" s="4" t="n"/>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>Verify case-insensitive search</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>1. Navigate to Groups tab.
 2. Type "hello" in search field.
 3. Observe results.</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>"Hello" group should appear regardless of case used in search.</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>GROUPS_014</t>
         </is>
       </c>
-      <c r="B13" s="4" t="n"/>
-      <c r="C13" s="4" t="n"/>
-      <c r="D13" s="4" t="n"/>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>Verify clearing search field</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>1. Navigate to Groups tab.
 2. Type search query.
 3. Clear the search field.</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>Full group list should be restored with all groups visible.</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>GROUPS_015</t>
         </is>
       </c>
-      <c r="B14" s="4" t="n"/>
-      <c r="C14" s="4" t="n"/>
-      <c r="D14" s="4" t="n"/>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>Verify real-time search filtering</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>1. Navigate to Groups tab.
 2. Start typing in search field.
 3. Observe list updates.</t>
         </is>
       </c>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>Group list should filter in real-time as user types each character.</t>
         </is>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>GROUPS_018</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>Verify Group selection</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>User is logged in and on Groups tab</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>Verify clicking on group opens conversation</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>1. Navigate to Groups tab.
 2. Click on any group (e.g., "Hiking Group").
 3. Observe result.</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>Group chat/conversation window should open.</t>
         </is>
       </c>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="H15" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>GROUPS_019</t>
         </is>
       </c>
-      <c r="B16" s="4" t="n"/>
-      <c r="C16" s="4" t="n"/>
-      <c r="D16" s="4" t="n"/>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>Verify selected group visual feedback</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>1. Navigate to Groups tab.
 2. Click on a group.
 3. Observe visual indication.</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr">
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>Selected group should show visual highlight (background color change).</t>
         </is>
       </c>
-      <c r="H16" s="4" t="inlineStr">
+      <c r="H16" s="5" t="inlineStr">
         <is>
           <t>Medium / Low</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>GROUPS_020</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>Verify Create Group button</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>User is logged in and on Groups tab</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>Verify Create Group button is visible</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>1. Navigate to Groups tab.
 2. Observe top right corner of Groups panel.</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>Create Group button (person+ icon) should be visible.</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="H17" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>GROUPS_021</t>
         </is>
       </c>
-      <c r="B18" s="4" t="n"/>
-      <c r="C18" s="4" t="n"/>
-      <c r="D18" s="4" t="n"/>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="5" t="n"/>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>Verify Create Group button click</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>1. Navigate to Groups tab.
 2. Click on Create Group button.
 3. Observe result.</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>Create Group dialog/screen should open.</t>
         </is>
       </c>
-      <c r="H18" s="4" t="inlineStr">
+      <c r="H18" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>GROUPS_022</t>
         </is>
       </c>
-      <c r="B19" s="4" t="n"/>
-      <c r="C19" s="4" t="n"/>
-      <c r="D19" s="4" t="n"/>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>Verify Create Group button hover state</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>1. Navigate to Groups tab.
 2. Hover over Create Group button.
 3. Observe visual feedback.</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>Button should show hover effect (color change, tooltip).</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr">
+      <c r="H19" s="5" t="inlineStr">
         <is>
           <t>Low / Low</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>GROUPS_023</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>Verify Welcome message panel</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>User is logged in, no group selected</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>Verify welcome message display</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>1. Navigate to Groups tab.
 2. Observe right panel without selecting any group.</t>
         </is>
       </c>
-      <c r="G20" s="4" t="inlineStr">
+      <c r="G20" s="5" t="inlineStr">
         <is>
           <t>Welcome message "Welcome to your Conversations" should display.</t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr">
+      <c r="H20" s="5" t="inlineStr">
         <is>
           <t>Medium / Low</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>GROUPS_024</t>
         </is>
       </c>
-      <c r="B21" s="4" t="n"/>
-      <c r="C21" s="4" t="n"/>
-      <c r="D21" s="4" t="n"/>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>Verify welcome message instruction text</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>1. Navigate to Groups tab.
 2. Read instruction text in right panel.</t>
         </is>
       </c>
-      <c r="G21" s="4" t="inlineStr">
+      <c r="G21" s="5" t="inlineStr">
         <is>
           <t>Instruction "Select a chat from the list to start exploring your messages or begin a new conversation." should display.</t>
         </is>
       </c>
-      <c r="H21" s="4" t="inlineStr">
+      <c r="H21" s="5" t="inlineStr">
         <is>
           <t>Low / Low</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>GROUPS_025</t>
         </is>
       </c>
-      <c r="B22" s="4" t="n"/>
-      <c r="C22" s="4" t="n"/>
-      <c r="D22" s="4" t="n"/>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="B22" s="5" t="n"/>
+      <c r="C22" s="5" t="n"/>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>Verify welcome message icon</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>1. Navigate to Groups tab.
 2. Observe icon in right panel.</t>
         </is>
       </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="G22" s="5" t="inlineStr">
         <is>
           <t>Chat bubble icon should display above the welcome message.</t>
         </is>
       </c>
-      <c r="H22" s="4" t="inlineStr">
+      <c r="H22" s="5" t="inlineStr">
         <is>
           <t>Low / Low</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>GROUPS_026</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>Verify UI responsiveness</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>Verify Groups module on desktop browser</t>
         </is>
       </c>
-      <c r="F23" s="4" t="inlineStr">
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>1. Open application on desktop.
 2. Navigate to Groups tab.
 3. Resize browser window.</t>
         </is>
       </c>
-      <c r="G23" s="4" t="inlineStr">
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>Layout should adjust dynamically; group list and welcome panel should remain functional.</t>
         </is>
       </c>
-      <c r="H23" s="4" t="inlineStr">
+      <c r="H23" s="5" t="inlineStr">
         <is>
           <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>GROUPS_027</t>
         </is>
       </c>
-      <c r="B24" s="4" t="n"/>
-      <c r="C24" s="4" t="n"/>
-      <c r="D24" s="4" t="n"/>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="B24" s="5" t="n"/>
+      <c r="C24" s="5" t="n"/>
+      <c r="D24" s="5" t="n"/>
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>Verify Groups module on mobile device</t>
         </is>
       </c>
-      <c r="F24" s="4" t="inlineStr">
+      <c r="F24" s="5" t="inlineStr">
         <is>
           <t>1. Open application on mobile browser/device.
 2. Navigate to Groups tab.
 3. Check layout.</t>
         </is>
       </c>
-      <c r="G24" s="4" t="inlineStr">
+      <c r="G24" s="5" t="inlineStr">
         <is>
           <t>Group list should fit screen properly; welcome panel may be hidden on mobile.</t>
         </is>
       </c>
-      <c r="H24" s="4" t="inlineStr">
+      <c r="H24" s="5" t="inlineStr">
         <is>
           <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>GROUPS_028</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>Verify navigation</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>Verify Groups tab highlight in navigation</t>
         </is>
       </c>
-      <c r="F25" s="4" t="inlineStr">
+      <c r="F25" s="5" t="inlineStr">
         <is>
           <t>1. Click on Groups tab in bottom navigation.
 2. Observe tab appearance.</t>
         </is>
       </c>
-      <c r="G25" s="4" t="inlineStr">
+      <c r="G25" s="5" t="inlineStr">
         <is>
           <t>Groups tab should be highlighted/selected (purple icon).</t>
         </is>
       </c>
-      <c r="H25" s="4" t="inlineStr">
+      <c r="H25" s="5" t="inlineStr">
         <is>
           <t>Medium / Low</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>GROUPS_029</t>
         </is>
       </c>
-      <c r="B26" s="4" t="n"/>
-      <c r="C26" s="4" t="n"/>
-      <c r="D26" s="4" t="n"/>
-      <c r="E26" s="4" t="inlineStr">
+      <c r="B26" s="5" t="n"/>
+      <c r="C26" s="5" t="n"/>
+      <c r="D26" s="5" t="n"/>
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>Verify navigation between tabs</t>
         </is>
       </c>
-      <c r="F26" s="4" t="inlineStr">
+      <c r="F26" s="5" t="inlineStr">
         <is>
           <t>1. Click on Groups tab.
 2. Click on Chats tab.
 3. Click back on Groups tab.</t>
         </is>
       </c>
-      <c r="G26" s="4" t="inlineStr">
+      <c r="G26" s="5" t="inlineStr">
         <is>
           <t>Navigation should work smoothly; Group list should reload correctly.</t>
         </is>
       </c>
-      <c r="H26" s="4" t="inlineStr">
+      <c r="H26" s="5" t="inlineStr">
         <is>
           <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>GROUPS_008</t>
         </is>
       </c>
-      <c r="B27" s="4" t="n"/>
-      <c r="C27" s="4" t="n"/>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="B27" s="5" t="n"/>
+      <c r="C27" s="5" t="n"/>
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>User is logged in, group has very long name</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>Verify handling of very long group names</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>1. Navigate to Groups tab.
 2. Find group with very long name.
 3. Observe display.</t>
         </is>
       </c>
-      <c r="G27" s="4" t="inlineStr">
+      <c r="G27" s="5" t="inlineStr">
         <is>
           <t>Long names should be truncated with ellipsis (...) without breaking layout.</t>
         </is>
       </c>
-      <c r="H27" s="4" t="inlineStr">
+      <c r="H27" s="5" t="inlineStr">
         <is>
           <t>Low / Medium</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>GROUPS_017</t>
         </is>
       </c>
-      <c r="B28" s="4" t="n"/>
-      <c r="C28" s="4" t="n"/>
-      <c r="D28" s="4" t="n"/>
-      <c r="E28" s="4" t="inlineStr">
+      <c r="B28" s="5" t="n"/>
+      <c r="C28" s="5" t="n"/>
+      <c r="D28" s="5" t="n"/>
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>Verify search with special characters</t>
         </is>
       </c>
-      <c r="F28" s="4" t="inlineStr">
+      <c r="F28" s="5" t="inlineStr">
         <is>
           <t>1. Navigate to Groups tab.
 2. Type "@#$%" in search field.
 3. Observe behavior.</t>
         </is>
       </c>
-      <c r="G28" s="4" t="inlineStr">
+      <c r="G28" s="5" t="inlineStr">
         <is>
           <t>Application should handle gracefully; show no results or ignore special characters.</t>
         </is>
       </c>
-      <c r="H28" s="4" t="inlineStr">
+      <c r="H28" s="5" t="inlineStr">
         <is>
           <t>Low / Medium</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>GROUPS_031</t>
         </is>
       </c>
-      <c r="B29" s="4" t="n"/>
-      <c r="C29" s="4" t="n"/>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="B29" s="5" t="n"/>
+      <c r="C29" s="5" t="n"/>
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>User is logged in, network error</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>Verify error handling on network failure</t>
         </is>
       </c>
-      <c r="F29" s="4" t="inlineStr">
+      <c r="F29" s="5" t="inlineStr">
         <is>
           <t>1. Disconnect network.
 2. Navigate to Groups tab.
 3. Observe error handling.</t>
         </is>
       </c>
-      <c r="G29" s="4" t="inlineStr">
+      <c r="G29" s="5" t="inlineStr">
         <is>
           <t>Appropriate error message should display with retry option.</t>
         </is>
       </c>
-      <c r="H29" s="4" t="inlineStr">
+      <c r="H29" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>GM_001</t>
         </is>
       </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>Join Password Group</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>Password protected group exists</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
+      <c r="E30" s="5" t="inlineStr">
         <is>
           <t>Verify password dialog appears for password group</t>
         </is>
       </c>
-      <c r="F30" s="4" t="inlineStr">
+      <c r="F30" s="5" t="inlineStr">
         <is>
           <t>1. Click on password protected group
 2. Check for dialog</t>
         </is>
       </c>
-      <c r="G30" s="4" t="inlineStr">
+      <c r="G30" s="5" t="inlineStr">
         <is>
           <t>Password input dialog appears</t>
         </is>
       </c>
-      <c r="H30" s="4" t="inlineStr">
+      <c r="H30" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>GM_002</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>Join Password Group - Correct</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>Password dialog open</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
+      <c r="E31" s="5" t="inlineStr">
         <is>
           <t>Verify joining with correct password</t>
         </is>
       </c>
-      <c r="F31" s="4" t="inlineStr">
+      <c r="F31" s="5" t="inlineStr">
         <is>
           <t>1. Enter correct password
 2. Click join</t>
         </is>
       </c>
-      <c r="G31" s="4" t="inlineStr">
+      <c r="G31" s="5" t="inlineStr">
         <is>
           <t>User joins group successfully</t>
         </is>
       </c>
-      <c r="H31" s="4" t="inlineStr">
+      <c r="H31" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>GM_003</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C32" s="5" t="inlineStr">
         <is>
           <t>Join Password Group - UI</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>Password dialog open</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
+      <c r="E32" s="5" t="inlineStr">
         <is>
           <t>Verify password dialog has input and join button</t>
         </is>
       </c>
-      <c r="F32" s="4" t="inlineStr">
+      <c r="F32" s="5" t="inlineStr">
         <is>
           <t>1. Check dialog elements</t>
         </is>
       </c>
-      <c r="G32" s="4" t="inlineStr">
+      <c r="G32" s="5" t="inlineStr">
         <is>
           <t>Password input field and Join button visible</t>
         </is>
       </c>
-      <c r="H32" s="4" t="inlineStr">
+      <c r="H32" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>GM_004</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>Group Type Icons in List</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>Groups list with mixed types</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr">
+      <c r="E33" s="5" t="inlineStr">
         <is>
           <t>Verify group type icons in groups list</t>
         </is>
       </c>
-      <c r="F33" s="4" t="inlineStr">
+      <c r="F33" s="5" t="inlineStr">
         <is>
           <t>1. Open groups list
 2. Check each group item</t>
         </is>
       </c>
-      <c r="G33" s="4" t="inlineStr">
+      <c r="G33" s="5" t="inlineStr">
         <is>
           <t>Public/private/password icons shown correctly</t>
         </is>
       </c>
-      <c r="H33" s="4" t="inlineStr">
+      <c r="H33" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>GM_005</t>
         </is>
       </c>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>Public Group Icon</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>Public group in list</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr">
+      <c r="E34" s="5" t="inlineStr">
         <is>
           <t>Verify public group has correct icon</t>
         </is>
       </c>
-      <c r="F34" s="4" t="inlineStr">
+      <c r="F34" s="5" t="inlineStr">
         <is>
           <t>1. Check public group item</t>
         </is>
       </c>
-      <c r="G34" s="4" t="inlineStr">
+      <c r="G34" s="5" t="inlineStr">
         <is>
           <t>Public/open icon displayed</t>
         </is>
       </c>
-      <c r="H34" s="4" t="inlineStr">
+      <c r="H34" s="5" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>GM_006</t>
         </is>
       </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>Private Group Icon</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>Private group in list</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr">
+      <c r="E35" s="5" t="inlineStr">
         <is>
           <t>Verify private group has lock icon</t>
         </is>
       </c>
-      <c r="F35" s="4" t="inlineStr">
+      <c r="F35" s="5" t="inlineStr">
         <is>
           <t>1. Check private group item</t>
         </is>
       </c>
-      <c r="G35" s="4" t="inlineStr">
+      <c r="G35" s="5" t="inlineStr">
         <is>
           <t>Lock/private icon displayed</t>
         </is>
       </c>
-      <c r="H35" s="4" t="inlineStr">
+      <c r="H35" s="5" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>GM_007</t>
         </is>
       </c>
-      <c r="B36" s="4" t="inlineStr">
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C36" s="4" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
         <is>
           <t>Password Group Icon</t>
         </is>
       </c>
-      <c r="D36" s="4" t="inlineStr">
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>Password group in list</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr">
+      <c r="E36" s="5" t="inlineStr">
         <is>
           <t>Verify password group has shield icon</t>
         </is>
       </c>
-      <c r="F36" s="4" t="inlineStr">
+      <c r="F36" s="5" t="inlineStr">
         <is>
           <t>1. Check password group item</t>
         </is>
       </c>
-      <c r="G36" s="4" t="inlineStr">
+      <c r="G36" s="5" t="inlineStr">
         <is>
           <t>Shield/password icon displayed</t>
         </is>
       </c>
-      <c r="H36" s="4" t="inlineStr">
+      <c r="H36" s="5" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="37"/>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>GRP_001</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Create Group - Open Dialog</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Groups tab active</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Verify create group dialog opens</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>1. Click create group button in groups header
+2. Observe dialog</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Create group dialog should appear with backdrop overlay</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>GRP_002</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>Create Group - Public Type Default</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>Create group dialog open</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>Verify Public is default group type</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>1. Open create group dialog
+2. Observe type selector</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>Public type should be selected by default</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>GRP_003</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>Create Group - Select Private Type</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>Create group dialog open</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>Verify selecting Private group type</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>1. Click Private option
+2. Observe selection</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>Private should be highlighted, no password field shown</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>GRP_004</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>Create Group - Select Password Type</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>Create group dialog open</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>Verify selecting Password group type shows password field</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>1. Click Password option
+2. Observe form</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>Password type selected, password input field should appear</t>
+        </is>
+      </c>
+      <c r="H40" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>GRP_005</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>Create Group - Enter Group Name</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>Create group dialog open</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>Verify entering group name</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>1. Type group name in name input
+2. Observe input</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>Group name should be accepted and displayed</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>GRP_006</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>Create Group - Create Public Group</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>Valid group name entered, Public type</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>Verify creating a public group</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>1. Enter group name
+2. Keep Public type
+3. Click Create Group</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>Group should be created via CometChat.createGroup(), dialog closes, group selected</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>GRP_007</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>Create Group - Create Private Group</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>Valid group name entered, Private type</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>Verify creating a private group</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>1. Enter group name
+2. Select Private
+3. Click Create Group</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>Private group should be created successfully</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>GRP_008</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Create Group - Create Password Group</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Valid name and password entered</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Verify creating a password-protected group</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>1. Enter group name
+2. Select Password type
+3. Enter password
+4. Click Create Group</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Password-protected group should be created successfully</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>GRP_009</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Create Group - Close Dialog</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Create group dialog open</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Verify closing the dialog</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>1. Click close button (X)
+2. Observe behavior</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>Dialog should close without creating a group</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>GRP_010</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Create Group - GUID Auto-Generation</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Creating a group</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Verify GUID is auto-generated with timestamp</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>1. Create a group
+2. Check generated GUID</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>GUID should be in format 'group_{timestamp}'</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>GRP_011</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Join Group - Dialog Display</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Password-protected group clicked</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Verify join group dialog appears</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>1. Click on a password-protected group
+2. Observe dialog</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>Dialog should show group avatar, name, member count, and password input</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>GRP_012</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Join Group - Auto-Focus Password</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Join group dialog displayed</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Verify password input auto-focuses</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>1. Open join group dialog
+2. Observe cursor position</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Password input should be auto-focused after 100ms delay</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>GRP_013</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Join Group - Enter Correct Password</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Join group dialog displayed</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Verify joining with correct password</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>1. Enter correct group password
+2. Click Continue</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>Should join group successfully, dialog closes, chat opens</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>GRP_014</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Join Group - Group Info Display</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Join group dialog displayed</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Verify group info is shown correctly</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>1. Open join group dialog
+2. Observe group info</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>Group avatar, name, and member count should be displayed</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>GRP_015</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Join Group - Close Dialog</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Join group dialog displayed</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Verify closing the dialog</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>1. Click close button
+2. Observe behavior</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>Dialog should close without joining the group</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>GROUPS_007</t>
         </is>
       </c>
-      <c r="B38" s="4" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C38" s="4" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
         <is>
           <t>Verify Group List display</t>
         </is>
       </c>
-      <c r="D38" s="4" t="inlineStr">
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>User is logged in, no groups exist</t>
         </is>
       </c>
-      <c r="E38" s="4" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>Verify empty group list state</t>
         </is>
       </c>
-      <c r="F38" s="4" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Groups tab with no groups.
 2. Observe display.</t>
         </is>
       </c>
-      <c r="G38" s="4" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr">
         <is>
           <t>Empty state message should display (e.g., "No groups found" or create group prompt).</t>
         </is>
       </c>
-      <c r="H38" s="4" t="inlineStr">
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="4" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>GROUPS_016</t>
         </is>
       </c>
-      <c r="B39" s="4" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C39" s="4" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
         <is>
           <t>Verify Group Search</t>
         </is>
       </c>
-      <c r="D39" s="4" t="inlineStr">
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>User is logged in and on Groups tab</t>
         </is>
       </c>
-      <c r="E39" s="4" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>Verify search with no matching results</t>
         </is>
       </c>
-      <c r="F39" s="4" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Groups tab.
 2. Type "XYZ123" in search field.
 3. Observe results.</t>
         </is>
       </c>
-      <c r="G39" s="4" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr">
         <is>
           <t>Empty state should display with message like "No groups found".</t>
         </is>
       </c>
-      <c r="H39" s="4" t="inlineStr">
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="4" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>GROUPS_030</t>
         </is>
       </c>
-      <c r="B40" s="4" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C40" s="4" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
         <is>
           <t>Verify Group List loading</t>
         </is>
       </c>
-      <c r="D40" s="4" t="inlineStr">
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>User is logged in, slow network</t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>Verify loading state during slow connection</t>
         </is>
       </c>
-      <c r="F40" s="4" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>1. Simulate slow network.
 2. Navigate to Groups tab.
 3. Observe loading behavior.</t>
         </is>
       </c>
-      <c r="G40" s="4" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr">
         <is>
           <t>Loading indicator should display while group list is being fetched.</t>
         </is>
       </c>
-      <c r="H40" s="4" t="inlineStr">
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="4" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>GM_008</t>
         </is>
       </c>
-      <c r="B41" s="4" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
         <is>
           <t>Join Password - Wrong Password</t>
         </is>
       </c>
-      <c r="D41" s="4" t="inlineStr">
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Password dialog open</t>
         </is>
       </c>
-      <c r="E41" s="4" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>Verify wrong password rejected</t>
         </is>
       </c>
-      <c r="F41" s="4" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>1. Enter incorrect password
 2. Click join</t>
         </is>
       </c>
-      <c r="G41" s="4" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>Error message shown, user not joined</t>
         </is>
       </c>
-      <c r="H41" s="4" t="inlineStr">
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="4" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>GM_009</t>
         </is>
       </c>
-      <c r="B42" s="4" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C42" s="4" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
         <is>
           <t>Join Password - Empty Password</t>
         </is>
       </c>
-      <c r="D42" s="4" t="inlineStr">
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Password dialog open</t>
         </is>
       </c>
-      <c r="E42" s="4" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>Verify empty password rejected</t>
         </is>
       </c>
-      <c r="F42" s="4" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>1. Leave password empty
 2. Click join</t>
         </is>
       </c>
-      <c r="G42" s="4" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr">
         <is>
           <t>Validation error, join button disabled or error shown</t>
         </is>
       </c>
-      <c r="H42" s="4" t="inlineStr">
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="4" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>GM_010</t>
         </is>
       </c>
-      <c r="B43" s="4" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C43" s="4" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
         <is>
           <t>Group Type Hidden</t>
         </is>
       </c>
-      <c r="D43" s="4" t="inlineStr">
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>hideGroupType=true in conversations</t>
         </is>
       </c>
-      <c r="E43" s="4" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>Verify group type icons hidden when configured</t>
         </is>
       </c>
-      <c r="F43" s="4" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>1. Set hideGroupType=true
 2. Check groups</t>
         </is>
       </c>
-      <c r="G43" s="4" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t>No group type icons visible</t>
         </is>
       </c>
-      <c r="H43" s="4" t="inlineStr">
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>GRP_016</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Create Group - Empty Name</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Create group dialog open</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>Verify validation for empty group name</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>1. Leave name field empty
+2. Click Create Group</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>Form should not submit due to required field validation</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>GRP_017</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Create Group - Password Type No Password</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Password type selected</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Verify validation when password is empty for password type</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>1. Select Password type
+2. Enter group name
+3. Leave password empty
+4. Click Create</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>Form should not submit due to required password field</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>GRP_018</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Create Group - API Failure</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Valid data entered, API error</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>Verify error handling on group creation failure</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>1. Enter valid data
+2. Simulate API failure
+3. Click Create</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>Error should be caught and logged, dialog should handle gracefully</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>GRP_019</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Create Group - Double Submit Prevention</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Valid data entered</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Verify double-click prevention on create</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>1. Enter valid data
+2. Click Create Group rapidly twice</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>Only one group should be created (isGroupCreated flag prevents double submit)</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>GRP_020</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Join Group - Wrong Password</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Join group dialog displayed</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>Verify wrong password error message</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>1. Enter incorrect password
+2. Click Continue</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>Wrong password error message should be displayed</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>GRP_021</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Join Group - Empty Password</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Join group dialog displayed</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>Verify empty password handling</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>1. Leave password empty
+2. Click Continue</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>Should attempt join with empty string, likely fail with wrong password error</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>GRP_022</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Join Group - Wrong Password Then Correct</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Wrong password error shown</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>Verify error clears on new input</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>1. Enter wrong password
+2. See error
+3. Start typing new password</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>Error message should disappear when user starts typing</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -2079,7 +3040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2135,208 +3096,336 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>GROUPS_032</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>Integration: Groups Module with Chat</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>User is logged in and on Groups tab</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>Verify clicking group opens group chat</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" s="5" t="inlineStr">
         <is>
           <t>1. Click on a group in the list.
 2. Observe chat area.</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>Group chat should open with message history and group header info.</t>
         </is>
       </c>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>GROUPS_033</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n"/>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>Integration: Groups Module with Group Actions</t>
         </is>
       </c>
-      <c r="D3" s="4" t="n"/>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>Verify group info accessible from group list</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>1. Long press or click info on a group in the list.</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>Group info/actions panel should open.</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>GM_011</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>Password Join + Conversation</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>Joined password group</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>Verify conversation created after joining</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>1. Join password group
 2. Check conversation list</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>New conversation appears for joined group</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>GM_012</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>Group Type + Details</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>Group with type icon</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>Verify type icon consistent in details view</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>1. Click group
 2. Check details</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>Same type icon shown in details</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
-    <row r="6"/>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>GRP_023</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Create Group - Event Emission</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Group created successfully</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Verify ccGroupCreated event is emitted</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1. Create a group
+2. Monitor events</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>CometChatGroupEvents.ccGroupCreated.next() should be called with created group</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>GRP_024</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Create Group - App State Update</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Group created successfully</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Verify app state updates with new group</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>1. Create a group
+2. Check app state</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>updateSelectedItemGroup should be dispatched with created group</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>GRP_025</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Join Group - Member Joined Event</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Successfully joined group</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Verify ccGroupMemberJoined event emitted</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1. Join a password group
+2. Monitor events</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>CometChatGroupEvents.ccGroupMemberJoined should fire after 100ms timeout</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>GM_013</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>Password Join + Network Loss</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Network drops during join</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Verify join fails gracefully on network loss</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>1. Enter password
 2. Disconnect
 3. Click join</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>Error shown, user not joined</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -2351,265 +3440,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00BF8F00"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>TestCase_ID</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>Sentiment</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Test Scenario</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Precondition</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Test Case</t>
-        </is>
-      </c>
-      <c r="F1" s="3" t="inlineStr">
-        <is>
-          <t>Steps</t>
-        </is>
-      </c>
-      <c r="G1" s="3" t="inlineStr">
-        <is>
-          <t>Expected Results</t>
-        </is>
-      </c>
-      <c r="H1" s="3" t="inlineStr">
-        <is>
-          <t>Priority/Severity</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>GROUPS_034</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>Regression: Groups Module</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>User is logged in</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>Verify group list updates after creating a new group</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>1. Create a new group.
-2. Go back to group list.</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>Newly created group should appear in the list.</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>GROUPS_035</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="n"/>
-      <c r="C3" s="4" t="n"/>
-      <c r="D3" s="4" t="n"/>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>Verify group list updates after leaving a group</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>1. Leave a group.
-2. Observe group list.</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>Left group should be removed from the list or marked appropriately.</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>GROUPS_036</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>Verify group list after deleting a group</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>1. Delete a group (as owner).
-2. Observe group list.</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>Deleted group should be removed from the list for all members.</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>GM_014</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Password After Group Type Change</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>Group type changed to password</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>Verify password dialog appears for changed group</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>1. Admin changes group to password type
-2. New user tries to join</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>Password dialog shown for newly password-protected group</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>GM_015</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Icon After Type Change</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>Group type changed</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>Verify icon updates after type change</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>1. Change group type
-2. Check list</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>Icon updated to reflect new type</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00C00000"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -2669,236 +3499,652 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>GROUPS_034</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Regression: Groups Module</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>Verify group list updates after creating a new group</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>1. Create a new group.
+2. Go back to group list.</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Newly created group should appear in the list.</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>GROUPS_035</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Verify group list updates after leaving a group</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>1. Leave a group.
+2. Observe group list.</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Left group should be removed from the list or marked appropriately.</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>GROUPS_036</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Verify group list after deleting a group</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>1. Delete a group (as owner).
+2. Observe group list.</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>Deleted group should be removed from the list for all members.</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>GM_014</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Password After Group Type Change</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Group type changed to password</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Verify password dialog appears for changed group</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>1. Admin changes group to password type
+2. New user tries to join</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>Password dialog shown for newly password-protected group</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="n"/>
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
+      <c r="G6" s="6" t="n"/>
+      <c r="H6" s="6" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>GM_015</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Icon After Type Change</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Group type changed</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Verify icon updates after type change</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>1. Change group type
+2. Check list</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>Icon updated to reflect new type</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="n"/>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n"/>
+      <c r="G8" s="6" t="n"/>
+      <c r="H8" s="6" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00C00000"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>TestCase_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Sentiment</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Precondition</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Expected Results</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Priority/Severity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>GROUPS_038</t>
         </is>
       </c>
-      <c r="B2" s="4" t="n"/>
-      <c r="C2" s="4" t="n"/>
-      <c r="D2" s="4" t="n"/>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="B2" s="5" t="n"/>
+      <c r="C2" s="5" t="n"/>
+      <c r="D2" s="5" t="n"/>
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>Verify password-protected group requires password to join</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" s="5" t="inlineStr">
         <is>
           <t>1. Click join on a password-protected group.
 2. Enter wrong password.</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>Should reject with 'Incorrect password' error. Should not allow entry.</t>
         </is>
       </c>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>High / Critical</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>GROUPS_039</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n"/>
-      <c r="C3" s="4" t="n"/>
-      <c r="D3" s="4" t="n"/>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>Verify group creation validates input</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>1. Try to create a group with empty name.
 2. Try with special characters.
 3. Try with very long name.</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>Empty name should be rejected. Special chars should be handled. Long name should truncate or reject.</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>GM_016</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>Password Not Visible</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>Typing password</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>Verify password field masks input</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>1. Type in password field
 2. Check display</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>Password characters masked (dots/asterisks)</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
-    <row r="5"/>
+    <row r="5">
+      <c r="A5" s="6" t="n"/>
+      <c r="B5" s="6" t="n"/>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="6" t="n"/>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
+      <c r="G5" s="6" t="n"/>
+      <c r="H5" s="6" t="n"/>
+    </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>GROUPS_037</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>Security: Groups Module</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>Verify private groups not visible to non-members</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>1. Observe group list as a non-member.</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>Private groups should not appear in the group list for non-members.</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>High / Critical</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>GM_017</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>Brute Force Password</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>Multiple wrong attempts</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>Verify rate limiting on password attempts</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>1. Enter wrong password 10+ times rapidly</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>Rate limiting or lockout after multiple failures</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>GM_018</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>Password in Network</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>Join request sent</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>Verify password encrypted in transit</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>1. Monitor network during join
 2. Check password</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>Password not visible in plain text in network</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>GRP_026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Create Group - XSS in Group Name</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Create group dialog open</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Verify XSS in group name</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>1. Enter &lt;script&gt;alert('xss')&lt;/script&gt; as name
+2. Create group</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Script should not execute, name treated as plain text</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>GRP_027</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Create Group - XSS in Password</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Password type selected</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Verify XSS in password field</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1. Enter &lt;img onerror=alert(1) src=x&gt; as password
+2. Create group</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Input should be sanitized, no script execution</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>GRP_028</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Join Group - Brute Force Password</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Join group dialog displayed</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Verify no rate limiting on password attempts</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1. Enter wrong password 10 times rapidly
+2. Observe behavior</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Each attempt should be processed (note: no client-side rate limiting exists)</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -2911,6 +4157,832 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00ED7D31"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>TestCase_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Sentiment</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Precondition</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Expected Results</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Priority/Severity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>GROUPS_040</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Edge Case: Groups Module</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>Verify group list with 500+ groups</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>1. Have an account that's part of 500+ groups.
+2. Open groups tab.</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Groups should load with pagination/infinite scroll. No performance issues.</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Medium / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>GROUPS_041</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Verify creating group with duplicate name</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>1. Create a group with a name that already exists.</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Should either allow (with different ID) or show warning about duplicate name.</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>GROUPS_042</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Verify group with emoji in name</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>1. Create a group named '🚀 Rocket Team'.
+2. Observe in group list.</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>Group name with emoji should display correctly.</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>Low / Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>GM_019</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Password with Special Chars</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Password has special characters</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Verify special character password works</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>1. Set password with !@#$%
+2. Join with same password</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>Join successful with special char password</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>GM_020</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Very Long Password</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Password with 100+ characters</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Verify long password handling</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>1. Enter 100+ char password
+2. Join</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>Long password accepted or appropriate limit shown</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>GRP_029</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Create Group - Switch Type Clears Password</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Password type with password entered</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Verify switching from Password to Public clears password context</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1. Select Password type
+2. Enter password
+3. Switch to Public
+4. Switch back to Password</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Password field should reappear (state preserved in component)</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="n"/>
+      <c r="B8" s="7" t="n"/>
+      <c r="C8" s="7" t="n"/>
+      <c r="D8" s="7" t="n"/>
+      <c r="E8" s="7" t="n"/>
+      <c r="F8" s="7" t="n"/>
+      <c r="G8" s="7" t="n"/>
+      <c r="H8" s="7" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>GROUPS_043</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Verify group creation without network</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>1. Disconnect network.
+2. Try to create a group.</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>Error message should display. Group should not be created.</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>GM_021</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Unicode Password</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Password with unicode/emoji</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Verify unicode password handling</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1. Enter emoji password
+2. Join</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Appropriate handling of unicode password</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>GRP_030</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Join Group - Very Long Password</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Join group dialog displayed</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Verify handling of extremely long password</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1. Enter 1000+ character password
+2. Click Continue</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Should handle gracefully, SDK processes the request</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="007030A0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>TestCase_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Sentiment</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Precondition</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Expected Results</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Priority/Severity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>GROUPS_044</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Boundary: Groups Module</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>Verify group list with exactly 0 groups</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>1. Login with account not part of any group.</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Empty state should display with 'No groups' message and create button.</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>GROUPS_045</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Verify group name with exactly 1 character</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>1. Create a group with name 'A'.</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Group should be created successfully with single character name.</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Low / Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>GROUPS_046</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Verify group name at maximum length</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>1. Create a group with name at max character limit.</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>Group should be created. Name should display (possibly truncated in list).</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>GM_022</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Password Min Length 1</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>1 character password</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Verify minimum password length</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>1. Set 1 char password
+2. Join with it</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>1 char password accepted</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>GRP_031</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Create Group - Single Char Name</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Create group dialog open</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Verify group creation with 1-character name</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1. Enter single character as name
+2. Create group</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Group should be created with single character name</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>GRP_032</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Join Group - Single Char Password</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Join group dialog, group has 1-char password</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Verify joining with minimum length password</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>1. Enter single character password
+2. Click Continue</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>Should join if password matches</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="n"/>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n"/>
+      <c r="G8" s="6" t="n"/>
+      <c r="H8" s="6" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>GM_023</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Password Max Length</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Very long password</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Verify password max length handling</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>1. Enter extremely long password</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Appropriate max length enforced</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>GRP_033</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Create Group - Very Long Name</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Create group dialog open</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Verify group creation with 500+ char name</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1. Enter 500+ character name
+2. Create group</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Should handle gracefully, SDK may have length limits</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="0000B0F0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -2970,824 +5042,285 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>GROUPS_040</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>GROUPS_047</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>Edge Case: Groups Module</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning: Group Types</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>Verify group list with 500+ groups</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>1. Have an account that's part of 500+ groups.
-2. Open groups tab.</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>Groups should load with pagination/infinite scroll. No performance issues.</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>Medium / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>GROUPS_041</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="n"/>
-      <c r="C3" s="4" t="n"/>
-      <c r="D3" s="4" t="n"/>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>Verify creating group with duplicate name</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>1. Create a group with a name that already exists.</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>Should either allow (with different ID) or show warning about duplicate name.</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>GROUPS_042</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>Verify group with emoji in name</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>1. Create a group named '🚀 Rocket Team'.
-2. Observe in group list.</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>Group name with emoji should display correctly.</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>Low / Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>GM_019</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Password with Special Chars</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>Password has special characters</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>Verify special character password works</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>1. Set password with !@#$%
-2. Join with same password</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>Join successful with special char password</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>GM_020</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Very Long Password</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>Password with 100+ characters</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>Verify long password handling</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>1. Enter 100+ char password
-2. Join</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>Long password accepted or appropriate limit shown</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>GROUPS_043</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="n"/>
-      <c r="D8" s="4" t="n"/>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>Verify group creation without network</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>1. Disconnect network.
-2. Try to create a group.</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>Error message should display. Group should not be created.</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>GM_021</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Unicode Password</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>Password with unicode/emoji</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>Verify unicode password handling</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>1. Enter emoji password
-2. Join</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>Appropriate handling of unicode password</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="007030A0"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>TestCase_ID</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>Sentiment</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Test Scenario</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Precondition</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Test Case</t>
-        </is>
-      </c>
-      <c r="F1" s="3" t="inlineStr">
-        <is>
-          <t>Steps</t>
-        </is>
-      </c>
-      <c r="G1" s="3" t="inlineStr">
-        <is>
-          <t>Expected Results</t>
-        </is>
-      </c>
-      <c r="H1" s="3" t="inlineStr">
-        <is>
-          <t>Priority/Severity</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>GROUPS_044</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>Boundary: Groups Module</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>User is logged in</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>Verify group list with exactly 0 groups</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>1. Login with account not part of any group.</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>Empty state should display with 'No groups' message and create button.</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>GROUPS_045</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="n"/>
-      <c r="C3" s="4" t="n"/>
-      <c r="D3" s="4" t="n"/>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>Verify group name with exactly 1 character</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>1. Create a group with name 'A'.</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>Group should be created successfully with single character name.</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>Low / Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>GROUPS_046</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>Verify group name at maximum length</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>1. Create a group with name at max character limit.</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>Group should be created. Name should display (possibly truncated in list).</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>GM_022</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Password Min Length 1</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>1 character password</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>Verify minimum password length</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>1. Set 1 char password
-2. Join with it</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>1 char password accepted</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>GM_023</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Password Max Length</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>Very long password</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>Verify password max length handling</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>1. Enter extremely long password</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>Appropriate max length enforced</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="0000B0F0"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>TestCase_ID</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>Sentiment</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Test Scenario</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Precondition</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Test Case</t>
-        </is>
-      </c>
-      <c r="F1" s="3" t="inlineStr">
-        <is>
-          <t>Steps</t>
-        </is>
-      </c>
-      <c r="G1" s="3" t="inlineStr">
-        <is>
-          <t>Expected Results</t>
-        </is>
-      </c>
-      <c r="H1" s="3" t="inlineStr">
-        <is>
-          <t>Priority/Severity</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>GROUPS_047</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning: Group Types</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>User is logged in</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>Verify public group display and join</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" s="5" t="inlineStr">
         <is>
           <t>1. Observe a public group in list.
 2. Click join.</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>Public group should show join button. Joining should be immediate without approval.</t>
         </is>
       </c>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>GROUPS_048</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n"/>
-      <c r="C3" s="4" t="n"/>
-      <c r="D3" s="4" t="n"/>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>Verify private group display and join</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>1. Observe a private group (if visible).
 2. Try to join.</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>Private group should require invitation. No direct join option.</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>GROUPS_049</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>Verify password-protected group display and join</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>1. Observe a password-protected group.
 2. Click join.
 3. Enter correct password.</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>Should prompt for password. Correct password should allow joining.</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>GM_024</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>Join Public Group</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>Public group</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>Verify direct join for public group</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>1. Click join on public group</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>User joins immediately without password</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>GM_025</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>Join Password Group</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>Password group</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>Verify password required for password group</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>1. Click join on password group</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>Password dialog shown before join</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
-    <row r="7"/>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>GRP_034</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Create Group - Unicode Name</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Create group dialog open</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Verify group creation with unicode name</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1. Enter unicode name (e.g., 日本語グループ)
+2. Create group</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Group should be created with unicode name</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="7" t="n"/>
+      <c r="B8" s="7" t="n"/>
+      <c r="C8" s="7" t="n"/>
+      <c r="D8" s="7" t="n"/>
+      <c r="E8" s="7" t="n"/>
+      <c r="F8" s="7" t="n"/>
+      <c r="G8" s="7" t="n"/>
+      <c r="H8" s="7" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>GM_026</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>Join Private Group</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Private group</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Verify cannot join private group directly</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>1. Try to join private group</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>Cannot join, must be invited</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
